--- a/assets/excel/2026_4-1-3.xlsx
+++ b/assets/excel/2026_4-1-3.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2A45F1-061D-4118-8B8F-B131AAC48920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC47C1A-FD32-483F-A27C-21E8ACA559FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{95AE330F-3948-45C2-BEAB-3D17B9280608}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{95AE330F-3948-45C2-BEAB-3D17B9280608}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -450,6 +447,55 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -501,55 +547,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -567,863 +564,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Download_4-3-1"/>
-      <sheetName val="CSV_Vorbereitung"/>
-      <sheetName val="CSV_Export"/>
-      <sheetName val="2021"/>
-      <sheetName val="2022"/>
-      <sheetName val="2023"/>
-      <sheetName val="2024"/>
-      <sheetName val="2025"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="7">
-          <cell r="D7">
-            <v>31.03</v>
-          </cell>
-          <cell r="E7">
-            <v>11.72</v>
-          </cell>
-          <cell r="F7">
-            <v>19.309999999999999</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>57.56</v>
-          </cell>
-          <cell r="E8">
-            <v>18.55</v>
-          </cell>
-          <cell r="F8">
-            <v>39.020000000000003</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>260.79000000000002</v>
-          </cell>
-          <cell r="E9">
-            <v>88.41</v>
-          </cell>
-          <cell r="F9">
-            <v>172.39</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="D11">
-            <v>56.47</v>
-          </cell>
-          <cell r="E11">
-            <v>35.57</v>
-          </cell>
-          <cell r="F11">
-            <v>20.9</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="D12">
-            <v>99.87</v>
-          </cell>
-          <cell r="E12">
-            <v>62.01</v>
-          </cell>
-          <cell r="F12">
-            <v>37.85</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="D13">
-            <v>888</v>
-          </cell>
-          <cell r="E13">
-            <v>680.57</v>
-          </cell>
-          <cell r="F13">
-            <v>207.43</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>178.91</v>
-          </cell>
-          <cell r="E15">
-            <v>130.76</v>
-          </cell>
-          <cell r="F15">
-            <v>48.15</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>307.37</v>
-          </cell>
-          <cell r="E16">
-            <v>238.17</v>
-          </cell>
-          <cell r="F16">
-            <v>69.209999999999994</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>1703.82</v>
-          </cell>
-          <cell r="E17">
-            <v>1355.05</v>
-          </cell>
-          <cell r="F17">
-            <v>348.77</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
-            <v>243.93</v>
-          </cell>
-          <cell r="E19">
-            <v>187.36</v>
-          </cell>
-          <cell r="F19">
-            <v>56.57</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20">
-            <v>468.26</v>
-          </cell>
-          <cell r="E20">
-            <v>342.44</v>
-          </cell>
-          <cell r="F20">
-            <v>125.82</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21">
-            <v>1873.8</v>
-          </cell>
-          <cell r="E21">
-            <v>1463.48</v>
-          </cell>
-          <cell r="F21">
-            <v>410.32</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="D24">
-            <v>510.35</v>
-          </cell>
-          <cell r="E24">
-            <v>365.41</v>
-          </cell>
-          <cell r="F24">
-            <v>144.94</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="D25">
-            <v>933.06</v>
-          </cell>
-          <cell r="E25">
-            <v>661.17</v>
-          </cell>
-          <cell r="F25">
-            <v>271.89999999999998</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="D26">
-            <v>4726.42</v>
-          </cell>
-          <cell r="E26">
-            <v>3587.51</v>
-          </cell>
-          <cell r="F26">
-            <v>1138.9100000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="7">
-          <cell r="D7">
-            <v>31.8</v>
-          </cell>
-          <cell r="E7">
-            <v>9.6</v>
-          </cell>
-          <cell r="F7">
-            <v>22.19</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>56.23</v>
-          </cell>
-          <cell r="E8">
-            <v>17.260000000000002</v>
-          </cell>
-          <cell r="F8">
-            <v>38.97</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>267.43</v>
-          </cell>
-          <cell r="E9">
-            <v>82.8</v>
-          </cell>
-          <cell r="F9">
-            <v>184.63</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="D11">
-            <v>56.3</v>
-          </cell>
-          <cell r="E11">
-            <v>33.119999999999997</v>
-          </cell>
-          <cell r="F11">
-            <v>23.18</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="D12">
-            <v>98.74</v>
-          </cell>
-          <cell r="E12">
-            <v>62.38</v>
-          </cell>
-          <cell r="F12">
-            <v>36.36</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="D13">
-            <v>840.02</v>
-          </cell>
-          <cell r="E13">
-            <v>633.41</v>
-          </cell>
-          <cell r="F13">
-            <v>206.61</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>179.52</v>
-          </cell>
-          <cell r="E15">
-            <v>134.29</v>
-          </cell>
-          <cell r="F15">
-            <v>45.22</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>308.45</v>
-          </cell>
-          <cell r="E16">
-            <v>237.73</v>
-          </cell>
-          <cell r="F16">
-            <v>70.72</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>1709.06</v>
-          </cell>
-          <cell r="E17">
-            <v>1356.72</v>
-          </cell>
-          <cell r="F17">
-            <v>352.34</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
-            <v>247.96</v>
-          </cell>
-          <cell r="E19">
-            <v>190.4</v>
-          </cell>
-          <cell r="F19">
-            <v>57.57</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20">
-            <v>480.67</v>
-          </cell>
-          <cell r="E20">
-            <v>343.99</v>
-          </cell>
-          <cell r="F20">
-            <v>136.66999999999999</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21">
-            <v>1940.14</v>
-          </cell>
-          <cell r="E21">
-            <v>1491.63</v>
-          </cell>
-          <cell r="F21">
-            <v>448.51</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="D24">
-            <v>515.58000000000004</v>
-          </cell>
-          <cell r="E24">
-            <v>367.42</v>
-          </cell>
-          <cell r="F24">
-            <v>148.16999999999999</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="D25">
-            <v>944.09</v>
-          </cell>
-          <cell r="E25">
-            <v>661.37</v>
-          </cell>
-          <cell r="F25">
-            <v>282.72000000000003</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="D26">
-            <v>4756.66</v>
-          </cell>
-          <cell r="E26">
-            <v>3564.56</v>
-          </cell>
-          <cell r="F26">
-            <v>1192.0899999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="7">
-          <cell r="D7">
-            <v>39.659999999999997</v>
-          </cell>
-          <cell r="E7">
-            <v>14.03</v>
-          </cell>
-          <cell r="F7">
-            <v>25.63</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>65.72</v>
-          </cell>
-          <cell r="E8">
-            <v>17.12</v>
-          </cell>
-          <cell r="F8">
-            <v>48.6</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>315.43</v>
-          </cell>
-          <cell r="E9">
-            <v>94.92</v>
-          </cell>
-          <cell r="F9">
-            <v>220.51</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="D11">
-            <v>66</v>
-          </cell>
-          <cell r="E11">
-            <v>38.31</v>
-          </cell>
-          <cell r="F11">
-            <v>27.69</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="D12">
-            <v>105.53</v>
-          </cell>
-          <cell r="E12">
-            <v>65.489999999999995</v>
-          </cell>
-          <cell r="F12">
-            <v>40.04</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="D13">
-            <v>887.08</v>
-          </cell>
-          <cell r="E13">
-            <v>654.65</v>
-          </cell>
-          <cell r="F13">
-            <v>232.43</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>167.88</v>
-          </cell>
-          <cell r="E15">
-            <v>118.76</v>
-          </cell>
-          <cell r="F15">
-            <v>49.11</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>300.25</v>
-          </cell>
-          <cell r="E16">
-            <v>232.17</v>
-          </cell>
-          <cell r="F16">
-            <v>68.08</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>1679.44</v>
-          </cell>
-          <cell r="E17">
-            <v>1332.12</v>
-          </cell>
-          <cell r="F17">
-            <v>347.32</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
-            <v>238.86</v>
-          </cell>
-          <cell r="E19">
-            <v>178.72</v>
-          </cell>
-          <cell r="F19">
-            <v>60.14</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20">
-            <v>481.9</v>
-          </cell>
-          <cell r="E20">
-            <v>353.29</v>
-          </cell>
-          <cell r="F20">
-            <v>128.61000000000001</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21">
-            <v>1895.85</v>
-          </cell>
-          <cell r="E21">
-            <v>1453.52</v>
-          </cell>
-          <cell r="F21">
-            <v>442.32</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="D24">
-            <v>512.4</v>
-          </cell>
-          <cell r="E24">
-            <v>349.82</v>
-          </cell>
-          <cell r="F24">
-            <v>162.58000000000001</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="D25">
-            <v>953.39</v>
-          </cell>
-          <cell r="E25">
-            <v>668.07</v>
-          </cell>
-          <cell r="F25">
-            <v>285.32</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="D26">
-            <v>4777.8</v>
-          </cell>
-          <cell r="E26">
-            <v>3535.21</v>
-          </cell>
-          <cell r="F26">
-            <v>1242.58</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="7">
-          <cell r="D7">
-            <v>38.39</v>
-          </cell>
-          <cell r="E7">
-            <v>13.96</v>
-          </cell>
-          <cell r="F7">
-            <v>24.43</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>73.099999999999994</v>
-          </cell>
-          <cell r="E8">
-            <v>17.23</v>
-          </cell>
-          <cell r="F8">
-            <v>55.87</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>331.44</v>
-          </cell>
-          <cell r="E9">
-            <v>94.9</v>
-          </cell>
-          <cell r="F9">
-            <v>236.54</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="D11">
-            <v>65.459999999999994</v>
-          </cell>
-          <cell r="E11">
-            <v>34.17</v>
-          </cell>
-          <cell r="F11">
-            <v>31.29</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="D12">
-            <v>101.68</v>
-          </cell>
-          <cell r="E12">
-            <v>59.39</v>
-          </cell>
-          <cell r="F12">
-            <v>42.28</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="D13">
-            <v>856.54</v>
-          </cell>
-          <cell r="E13">
-            <v>603.1</v>
-          </cell>
-          <cell r="F13">
-            <v>253.44</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>160.22999999999999</v>
-          </cell>
-          <cell r="E15">
-            <v>108.81</v>
-          </cell>
-          <cell r="F15">
-            <v>51.43</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>280.98</v>
-          </cell>
-          <cell r="E16">
-            <v>209.46</v>
-          </cell>
-          <cell r="F16">
-            <v>71.52</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>1634.44</v>
-          </cell>
-          <cell r="E17">
-            <v>1263.5899999999999</v>
-          </cell>
-          <cell r="F17">
-            <v>370.85</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
-            <v>237.92</v>
-          </cell>
-          <cell r="E19">
-            <v>173.16</v>
-          </cell>
-          <cell r="F19">
-            <v>64.760000000000005</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20">
-            <v>509.1</v>
-          </cell>
-          <cell r="E20">
-            <v>375.39</v>
-          </cell>
-          <cell r="F20">
-            <v>133.71</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21">
-            <v>1951.39</v>
-          </cell>
-          <cell r="E21">
-            <v>1476.93</v>
-          </cell>
-          <cell r="F21">
-            <v>474.46</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="D24">
-            <v>502</v>
-          </cell>
-          <cell r="E24">
-            <v>330.09</v>
-          </cell>
-          <cell r="F24">
-            <v>171.91</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="D25">
-            <v>964.86</v>
-          </cell>
-          <cell r="E25">
-            <v>661.48</v>
-          </cell>
-          <cell r="F25">
-            <v>303.38</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="D26">
-            <v>4773.8100000000004</v>
-          </cell>
-          <cell r="E26">
-            <v>3438.52</v>
-          </cell>
-          <cell r="F26">
-            <v>1335.29</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="7">
-          <cell r="D7">
-            <v>37.76</v>
-          </cell>
-          <cell r="E7">
-            <v>10.119999999999999</v>
-          </cell>
-          <cell r="F7">
-            <v>27.64</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>67.33</v>
-          </cell>
-          <cell r="E8">
-            <v>14.42</v>
-          </cell>
-          <cell r="F8">
-            <v>52.91</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>325.64</v>
-          </cell>
-          <cell r="E9">
-            <v>85.93</v>
-          </cell>
-          <cell r="F9">
-            <v>239.71</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="D11">
-            <v>59.67</v>
-          </cell>
-          <cell r="E11">
-            <v>32.270000000000003</v>
-          </cell>
-          <cell r="F11">
-            <v>27.4</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="D12">
-            <v>95.83</v>
-          </cell>
-          <cell r="E12">
-            <v>55.59</v>
-          </cell>
-          <cell r="F12">
-            <v>40.229999999999997</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="D13">
-            <v>810.46</v>
-          </cell>
-          <cell r="E13">
-            <v>560.63</v>
-          </cell>
-          <cell r="F13">
-            <v>249.83</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>158.87</v>
-          </cell>
-          <cell r="E15">
-            <v>105.61</v>
-          </cell>
-          <cell r="F15">
-            <v>53.26</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>273.69</v>
-          </cell>
-          <cell r="E16">
-            <v>202.26</v>
-          </cell>
-          <cell r="F16">
-            <v>71.430000000000007</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>1598.94</v>
-          </cell>
-          <cell r="E17">
-            <v>1230.8800000000001</v>
-          </cell>
-          <cell r="F17">
-            <v>368.06</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
-            <v>227.52</v>
-          </cell>
-          <cell r="E19">
-            <v>161.57</v>
-          </cell>
-          <cell r="F19">
-            <v>65.94</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20">
-            <v>511.94</v>
-          </cell>
-          <cell r="E20">
-            <v>368.59</v>
-          </cell>
-          <cell r="F20">
-            <v>143.35</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21">
-            <v>2005.76</v>
-          </cell>
-          <cell r="E21">
-            <v>1512.21</v>
-          </cell>
-          <cell r="F21">
-            <v>493.55</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="D24">
-            <v>483.81</v>
-          </cell>
-          <cell r="E24">
-            <v>309.57</v>
-          </cell>
-          <cell r="F24">
-            <v>174.24</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="D25">
-            <v>948.78</v>
-          </cell>
-          <cell r="E25">
-            <v>640.86</v>
-          </cell>
-          <cell r="F25">
-            <v>307.92</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="D26">
-            <v>4740.8</v>
-          </cell>
-          <cell r="E26">
-            <v>3389.65</v>
-          </cell>
-          <cell r="F26">
-            <v>1351.15</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1773,28 +913,28 @@
       <c r="L4" s="1"/>
     </row>
     <row r="6" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="54"/>
     </row>
     <row r="7" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="23"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="32"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="8" t="s">
         <v>7</v>
       </c>
@@ -1803,24 +943,24 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="23"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="36" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="53"/>
     </row>
     <row r="9" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="37" t="s">
+      <c r="B9" s="43"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
     </row>
     <row r="10" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
@@ -1842,7 +982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>11</v>
       </c>
@@ -1853,19 +993,16 @@
         <v>2025</v>
       </c>
       <c r="E11" s="15">
-        <f>'[1]2025'!D7/'[1]2025'!D24*100</f>
         <v>7.8047167276410159</v>
       </c>
       <c r="F11" s="15">
-        <f>'[1]2025'!F7/'[1]2025'!F24*100</f>
         <v>15.86317722681359</v>
       </c>
       <c r="G11" s="15">
-        <f>'[1]2025'!E7/'[1]2025'!E24*100</f>
         <v>3.269050618599993</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>13</v>
       </c>
@@ -1876,19 +1013,16 @@
         <v>2025</v>
       </c>
       <c r="E12" s="15">
-        <f>'[1]2025'!D8/'[1]2025'!D25*100</f>
         <v>7.0964817976770167</v>
       </c>
       <c r="F12" s="15">
-        <f>'[1]2025'!F8/'[1]2025'!F25*100</f>
         <v>17.183034554429721</v>
       </c>
       <c r="G12" s="15">
-        <f>'[1]2025'!E8/'[1]2025'!E25*100</f>
         <v>2.2501014262085324</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>14</v>
       </c>
@@ -1899,19 +1033,16 @@
         <v>2025</v>
       </c>
       <c r="E13" s="15">
-        <f>'[1]2025'!D9/'[1]2025'!D26*100</f>
         <v>6.8688828889638867</v>
       </c>
       <c r="F13" s="15">
-        <f>'[1]2025'!F9/'[1]2025'!F26*100</f>
         <v>17.741183436332015</v>
       </c>
       <c r="G13" s="15">
-        <f>'[1]2025'!E9/'[1]2025'!E26*100</f>
         <v>2.5350699924770996</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
         <v>11</v>
       </c>
@@ -1922,19 +1053,16 @@
         <v>2025</v>
       </c>
       <c r="E14" s="15">
-        <f>'[1]2025'!D11/'[1]2025'!D24*100</f>
         <v>12.333354002604329</v>
       </c>
       <c r="F14" s="15">
-        <f>'[1]2025'!F11/'[1]2025'!F24*100</f>
         <v>15.725436179981633</v>
       </c>
       <c r="G14" s="15">
-        <f>'[1]2025'!E11/'[1]2025'!E24*100</f>
         <v>10.424136705753142</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1945,19 +1073,16 @@
         <v>2025</v>
       </c>
       <c r="E15" s="15">
-        <f>'[1]2025'!D12/'[1]2025'!D25*100</f>
         <v>10.10033938320791</v>
       </c>
       <c r="F15" s="15">
-        <f>'[1]2025'!F12/'[1]2025'!F25*100</f>
         <v>13.065081839438813</v>
       </c>
       <c r="G15" s="15">
-        <f>'[1]2025'!E12/'[1]2025'!E25*100</f>
         <v>8.67428143432263</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1968,19 +1093,16 @@
         <v>2025</v>
       </c>
       <c r="E16" s="15">
-        <f>'[1]2025'!D13/'[1]2025'!D26*100</f>
         <v>17.095426932163349</v>
       </c>
       <c r="F16" s="15">
-        <f>'[1]2025'!F13/'[1]2025'!F26*100</f>
         <v>18.490175036080377</v>
       </c>
       <c r="G16" s="15">
-        <f>'[1]2025'!E13/'[1]2025'!E26*100</f>
         <v>16.539465726549938</v>
       </c>
     </row>
-    <row r="17" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
         <v>11</v>
       </c>
@@ -1991,19 +1113,16 @@
         <v>2025</v>
       </c>
       <c r="E17" s="15">
-        <f>'[1]2025'!D15/'[1]2025'!D24*100</f>
         <v>32.837270829457843</v>
       </c>
       <c r="F17" s="15">
-        <f>'[1]2025'!F15/'[1]2025'!F24*100</f>
         <v>30.567033976124879</v>
       </c>
       <c r="G17" s="15">
-        <f>'[1]2025'!E15/'[1]2025'!E24*100</f>
         <v>34.11506282908551</v>
       </c>
     </row>
-    <row r="18" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>13</v>
       </c>
@@ -2014,19 +1133,16 @@
         <v>2025</v>
       </c>
       <c r="E18" s="15">
-        <f>'[1]2025'!D16/'[1]2025'!D25*100</f>
         <v>28.846518687156138</v>
       </c>
       <c r="F18" s="15">
-        <f>'[1]2025'!F16/'[1]2025'!F25*100</f>
         <v>23.197583787996884</v>
       </c>
       <c r="G18" s="15">
-        <f>'[1]2025'!E16/'[1]2025'!E25*100</f>
         <v>31.560715288830632</v>
       </c>
     </row>
-    <row r="19" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
         <v>14</v>
       </c>
@@ -2037,19 +1153,16 @@
         <v>2025</v>
       </c>
       <c r="E19" s="15">
-        <f>'[1]2025'!D17/'[1]2025'!D26*100</f>
         <v>33.727219034762065</v>
       </c>
       <c r="F19" s="15">
-        <f>'[1]2025'!F17/'[1]2025'!F26*100</f>
         <v>27.240498834326317</v>
       </c>
       <c r="G19" s="15">
-        <f>'[1]2025'!E17/'[1]2025'!E26*100</f>
         <v>36.312893661587481</v>
       </c>
     </row>
-    <row r="20" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
         <v>11</v>
       </c>
@@ -2060,19 +1173,16 @@
         <v>2025</v>
       </c>
       <c r="E20" s="15">
-        <f>'[1]2025'!D19/'[1]2025'!D24*100</f>
         <v>47.026725367396295</v>
       </c>
       <c r="F20" s="15">
-        <f>'[1]2025'!F19/'[1]2025'!F24*100</f>
         <v>37.844352617079885</v>
       </c>
       <c r="G20" s="15">
-        <f>'[1]2025'!E19/'[1]2025'!E24*100</f>
         <v>52.191749846561351</v>
       </c>
     </row>
-    <row r="21" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
         <v>13</v>
       </c>
@@ -2083,19 +1193,16 @@
         <v>2025</v>
       </c>
       <c r="E21" s="15">
-        <f>'[1]2025'!D20/'[1]2025'!D25*100</f>
         <v>53.957714117076669</v>
       </c>
       <c r="F21" s="15">
-        <f>'[1]2025'!F20/'[1]2025'!F25*100</f>
         <v>46.554299818134574</v>
       </c>
       <c r="G21" s="15">
-        <f>'[1]2025'!E20/'[1]2025'!E25*100</f>
         <v>57.514901850638203</v>
       </c>
     </row>
-    <row r="22" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="13" t="s">
         <v>14</v>
       </c>
@@ -2106,19 +1213,16 @@
         <v>2025</v>
       </c>
       <c r="E22" s="15">
-        <f>'[1]2025'!D21/'[1]2025'!D26*100</f>
         <v>42.308471144110698</v>
       </c>
       <c r="F22" s="15">
-        <f>'[1]2025'!F21/'[1]2025'!F26*100</f>
         <v>36.528142693261294</v>
       </c>
       <c r="G22" s="15">
-        <f>'[1]2025'!E21/'[1]2025'!E26*100</f>
         <v>44.61257061938548</v>
       </c>
     </row>
-    <row r="23" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="13" t="s">
         <v>11</v>
       </c>
@@ -2129,19 +1233,16 @@
         <v>2024</v>
       </c>
       <c r="E23" s="15">
-        <f>'[1]2024'!D7/'[1]2024'!D24*100</f>
         <v>7.6474103585657369</v>
       </c>
       <c r="F23" s="15">
-        <f>'[1]2024'!F7/'[1]2024'!F24*100</f>
         <v>14.210924320865569</v>
       </c>
       <c r="G23" s="15">
-        <f>'[1]2024'!E7/'[1]2024'!E24*100</f>
         <v>4.2291496258596153</v>
       </c>
     </row>
-    <row r="24" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
         <v>13</v>
       </c>
@@ -2152,19 +1253,16 @@
         <v>2024</v>
       </c>
       <c r="E24" s="15">
-        <f>'[1]2024'!D8/'[1]2024'!D25*100</f>
         <v>7.5762286756627901</v>
       </c>
       <c r="F24" s="15">
-        <f>'[1]2024'!F8/'[1]2024'!F25*100</f>
         <v>18.415848111279583</v>
       </c>
       <c r="G24" s="15">
-        <f>'[1]2024'!E8/'[1]2024'!E25*100</f>
         <v>2.6047650722621998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="13" t="s">
         <v>14</v>
       </c>
@@ -2175,19 +1273,16 @@
         <v>2024</v>
       </c>
       <c r="E25" s="15">
-        <f>'[1]2024'!D9/'[1]2024'!D26*100</f>
         <v>6.9428821004606371</v>
       </c>
       <c r="F25" s="15">
-        <f>'[1]2024'!F9/'[1]2024'!F26*100</f>
         <v>17.71450396543073</v>
       </c>
       <c r="G25" s="15">
-        <f>'[1]2024'!E9/'[1]2024'!E26*100</f>
         <v>2.7599083326547471</v>
       </c>
     </row>
-    <row r="26" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>11</v>
       </c>
@@ -2198,19 +1293,16 @@
         <v>2024</v>
       </c>
       <c r="E26" s="15">
-        <f>'[1]2024'!D11/'[1]2024'!D24*100</f>
         <v>13.039840637450197</v>
       </c>
       <c r="F26" s="15">
-        <f>'[1]2024'!F11/'[1]2024'!F24*100</f>
         <v>18.201384445349312</v>
       </c>
       <c r="G26" s="15">
-        <f>'[1]2024'!E11/'[1]2024'!E24*100</f>
         <v>10.351722257566118</v>
       </c>
     </row>
-    <row r="27" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
         <v>13</v>
       </c>
@@ -2221,19 +1313,16 @@
         <v>2024</v>
       </c>
       <c r="E27" s="15">
-        <f>'[1]2024'!D12/'[1]2024'!D25*100</f>
         <v>10.538316439690734</v>
       </c>
       <c r="F27" s="15">
-        <f>'[1]2024'!F12/'[1]2024'!F25*100</f>
         <v>13.936317489616984</v>
       </c>
       <c r="G27" s="15">
-        <f>'[1]2024'!E12/'[1]2024'!E25*100</f>
         <v>8.9783515752554877</v>
       </c>
     </row>
-    <row r="28" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
         <v>14</v>
       </c>
@@ -2244,19 +1333,16 @@
         <v>2024</v>
       </c>
       <c r="E28" s="15">
-        <f>'[1]2024'!D13/'[1]2024'!D26*100</f>
         <v>17.942482000749923</v>
       </c>
       <c r="F28" s="15">
-        <f>'[1]2024'!F13/'[1]2024'!F26*100</f>
         <v>18.980146634813412</v>
       </c>
       <c r="G28" s="15">
-        <f>'[1]2024'!E13/'[1]2024'!E26*100</f>
         <v>17.539522817956563</v>
       </c>
     </row>
-    <row r="29" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
         <v>11</v>
       </c>
@@ -2267,19 +1353,16 @@
         <v>2024</v>
       </c>
       <c r="E29" s="15">
-        <f>'[1]2024'!D15/'[1]2024'!D24*100</f>
         <v>31.91832669322709</v>
       </c>
       <c r="F29" s="15">
-        <f>'[1]2024'!F15/'[1]2024'!F24*100</f>
         <v>29.916816939096041</v>
       </c>
       <c r="G29" s="15">
-        <f>'[1]2024'!E15/'[1]2024'!E24*100</f>
         <v>32.963737162592025</v>
       </c>
     </row>
-    <row r="30" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="13" t="s">
         <v>13</v>
       </c>
@@ -2290,19 +1373,16 @@
         <v>2024</v>
       </c>
       <c r="E30" s="15">
-        <f>'[1]2024'!D16/'[1]2024'!D25*100</f>
         <v>29.121323300789754</v>
       </c>
       <c r="F30" s="15">
-        <f>'[1]2024'!F16/'[1]2024'!F25*100</f>
         <v>23.574395147999208</v>
       </c>
       <c r="G30" s="15">
-        <f>'[1]2024'!E16/'[1]2024'!E25*100</f>
         <v>31.66535647336276</v>
       </c>
     </row>
-    <row r="31" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="13" t="s">
         <v>14</v>
       </c>
@@ -2313,19 +1393,16 @@
         <v>2024</v>
       </c>
       <c r="E31" s="15">
-        <f>'[1]2024'!D17/'[1]2024'!D26*100</f>
         <v>34.237642470060599</v>
       </c>
       <c r="F31" s="15">
-        <f>'[1]2024'!F17/'[1]2024'!F26*100</f>
         <v>27.772993132577945</v>
       </c>
       <c r="G31" s="15">
-        <f>'[1]2024'!E17/'[1]2024'!E26*100</f>
         <v>36.7480776613194</v>
       </c>
     </row>
-    <row r="32" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
         <v>11</v>
       </c>
@@ -2336,19 +1413,16 @@
         <v>2024</v>
       </c>
       <c r="E32" s="15">
-        <f>'[1]2024'!D19/'[1]2024'!D24*100</f>
         <v>47.394422310756966</v>
       </c>
       <c r="F32" s="15">
-        <f>'[1]2024'!F19/'[1]2024'!F24*100</f>
         <v>37.670874294689085</v>
       </c>
       <c r="G32" s="15">
-        <f>'[1]2024'!E19/'[1]2024'!E24*100</f>
         <v>52.458420430791605</v>
       </c>
     </row>
-    <row r="33" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="13" t="s">
         <v>13</v>
       </c>
@@ -2359,19 +1433,16 @@
         <v>2024</v>
       </c>
       <c r="E33" s="15">
-        <f>'[1]2024'!D20/'[1]2024'!D25*100</f>
         <v>52.764131583856724</v>
       </c>
       <c r="F33" s="15">
-        <f>'[1]2024'!F20/'[1]2024'!F25*100</f>
         <v>44.073439251104233</v>
       </c>
       <c r="G33" s="15">
-        <f>'[1]2024'!E20/'[1]2024'!E25*100</f>
         <v>56.750015117615035</v>
       </c>
     </row>
-    <row r="34" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
         <v>14</v>
       </c>
@@ -2382,19 +1453,16 @@
         <v>2024</v>
       </c>
       <c r="E34" s="15">
-        <f>'[1]2024'!D21/'[1]2024'!D26*100</f>
         <v>40.876993428728838</v>
       </c>
       <c r="F34" s="15">
-        <f>'[1]2024'!F21/'[1]2024'!F26*100</f>
         <v>35.532356267177917</v>
       </c>
       <c r="G34" s="15">
-        <f>'[1]2024'!E21/'[1]2024'!E26*100</f>
         <v>42.952491188069288</v>
       </c>
     </row>
-    <row r="35" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="s">
         <v>11</v>
       </c>
@@ -2405,19 +1473,16 @@
         <v>2023</v>
       </c>
       <c r="E35" s="15">
-        <f>'[1]2023'!D7/'[1]2023'!D24*100</f>
         <v>7.7400468384074941</v>
       </c>
       <c r="F35" s="15">
-        <f>'[1]2023'!F7/'[1]2023'!F24*100</f>
         <v>15.764546684709064</v>
       </c>
       <c r="G35" s="15">
-        <f>'[1]2023'!E7/'[1]2023'!E24*100</f>
         <v>4.010634040363616</v>
       </c>
     </row>
-    <row r="36" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="s">
         <v>13</v>
       </c>
@@ -2428,19 +1493,16 @@
         <v>2023</v>
       </c>
       <c r="E36" s="15">
-        <f>'[1]2023'!D8/'[1]2023'!D25*100</f>
         <v>6.8932965523028358</v>
       </c>
       <c r="F36" s="15">
-        <f>'[1]2023'!F8/'[1]2023'!F25*100</f>
         <v>17.033506238609281</v>
       </c>
       <c r="G36" s="15">
-        <f>'[1]2023'!E8/'[1]2023'!E25*100</f>
         <v>2.5626057149699881</v>
       </c>
     </row>
-    <row r="37" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="s">
         <v>14</v>
       </c>
@@ -2451,19 +1513,16 @@
         <v>2023</v>
       </c>
       <c r="E37" s="15">
-        <f>'[1]2023'!D9/'[1]2023'!D26*100</f>
         <v>6.6019925488718654</v>
       </c>
       <c r="F37" s="15">
-        <f>'[1]2023'!F9/'[1]2023'!F26*100</f>
         <v>17.7461410935312</v>
       </c>
       <c r="G37" s="15">
-        <f>'[1]2023'!E9/'[1]2023'!E26*100</f>
         <v>2.6849890105538283</v>
       </c>
     </row>
-    <row r="38" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="s">
         <v>11</v>
       </c>
@@ -2474,19 +1533,16 @@
         <v>2023</v>
       </c>
       <c r="E38" s="15">
-        <f>'[1]2023'!D11/'[1]2023'!D24*100</f>
         <v>12.880562060889931</v>
       </c>
       <c r="F38" s="15">
-        <f>'[1]2023'!F11/'[1]2023'!F24*100</f>
         <v>17.031615204822241</v>
       </c>
       <c r="G38" s="15">
-        <f>'[1]2023'!E11/'[1]2023'!E24*100</f>
         <v>10.951346406723458</v>
       </c>
     </row>
-    <row r="39" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13" t="s">
         <v>13</v>
       </c>
@@ -2497,19 +1553,16 @@
         <v>2023</v>
       </c>
       <c r="E39" s="15">
-        <f>'[1]2023'!D12/'[1]2023'!D25*100</f>
         <v>11.068922476636004</v>
       </c>
       <c r="F39" s="15">
-        <f>'[1]2023'!F12/'[1]2023'!F25*100</f>
         <v>14.033366045142296</v>
       </c>
       <c r="G39" s="15">
-        <f>'[1]2023'!E12/'[1]2023'!E25*100</f>
         <v>9.8028649692397476</v>
       </c>
     </row>
-    <row r="40" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="s">
         <v>14</v>
       </c>
@@ -2520,19 +1573,16 @@
         <v>2023</v>
       </c>
       <c r="E40" s="15">
-        <f>'[1]2023'!D13/'[1]2023'!D26*100</f>
         <v>18.566704340910043</v>
       </c>
       <c r="F40" s="15">
-        <f>'[1]2023'!F13/'[1]2023'!F26*100</f>
         <v>18.705435464919766</v>
       </c>
       <c r="G40" s="15">
-        <f>'[1]2023'!E13/'[1]2023'!E26*100</f>
         <v>18.517994687727178</v>
       </c>
     </row>
-    <row r="41" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="13" t="s">
         <v>11</v>
       </c>
@@ -2543,19 +1593,16 @@
         <v>2023</v>
       </c>
       <c r="E41" s="15">
-        <f>'[1]2023'!D15/'[1]2023'!D24*100</f>
         <v>32.763466042154562</v>
       </c>
       <c r="F41" s="15">
-        <f>'[1]2023'!F15/'[1]2023'!F24*100</f>
         <v>30.206667486775739</v>
       </c>
       <c r="G41" s="15">
-        <f>'[1]2023'!E15/'[1]2023'!E24*100</f>
         <v>33.948887999542627</v>
       </c>
     </row>
-    <row r="42" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="13" t="s">
         <v>13</v>
       </c>
@@ -2566,19 +1613,16 @@
         <v>2023</v>
       </c>
       <c r="E42" s="15">
-        <f>'[1]2023'!D16/'[1]2023'!D25*100</f>
         <v>31.492883290154083</v>
       </c>
       <c r="F42" s="15">
-        <f>'[1]2023'!F16/'[1]2023'!F25*100</f>
         <v>23.860928080751435</v>
       </c>
       <c r="G42" s="15">
-        <f>'[1]2023'!E16/'[1]2023'!E25*100</f>
         <v>34.752346311015309</v>
       </c>
     </row>
-    <row r="43" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="13" t="s">
         <v>14</v>
       </c>
@@ -2589,19 +1633,16 @@
         <v>2023</v>
       </c>
       <c r="E43" s="15">
-        <f>'[1]2023'!D17/'[1]2023'!D26*100</f>
         <v>35.150906274854535</v>
       </c>
       <c r="F43" s="15">
-        <f>'[1]2023'!F17/'[1]2023'!F26*100</f>
         <v>27.951520224049965</v>
       </c>
       <c r="G43" s="15">
-        <f>'[1]2023'!E17/'[1]2023'!E26*100</f>
         <v>37.681495583006381</v>
       </c>
     </row>
-    <row r="44" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="13" t="s">
         <v>11</v>
       </c>
@@ -2612,19 +1653,16 @@
         <v>2023</v>
       </c>
       <c r="E44" s="15">
-        <f>'[1]2023'!D19/'[1]2023'!D24*100</f>
         <v>46.615925058548015</v>
       </c>
       <c r="F44" s="15">
-        <f>'[1]2023'!F19/'[1]2023'!F24*100</f>
         <v>36.991019805634146</v>
       </c>
       <c r="G44" s="15">
-        <f>'[1]2023'!E19/'[1]2023'!E24*100</f>
         <v>51.089131553370301</v>
       </c>
     </row>
-    <row r="45" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>13</v>
       </c>
@@ -2635,19 +1673,16 @@
         <v>2023</v>
       </c>
       <c r="E45" s="15">
-        <f>'[1]2023'!D20/'[1]2023'!D25*100</f>
         <v>50.545946569609498</v>
       </c>
       <c r="F45" s="15">
-        <f>'[1]2023'!F20/'[1]2023'!F25*100</f>
         <v>45.075704472171601</v>
       </c>
       <c r="G45" s="15">
-        <f>'[1]2023'!E20/'[1]2023'!E25*100</f>
         <v>52.882183004774951</v>
       </c>
     </row>
-    <row r="46" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="13" t="s">
         <v>14</v>
       </c>
@@ -2658,19 +1693,16 @@
         <v>2023</v>
       </c>
       <c r="E46" s="15">
-        <f>'[1]2023'!D21/'[1]2023'!D26*100</f>
         <v>39.680396835363553</v>
       </c>
       <c r="F46" s="15">
-        <f>'[1]2023'!F21/'[1]2023'!F26*100</f>
         <v>35.596903217499076</v>
       </c>
       <c r="G46" s="15">
-        <f>'[1]2023'!E21/'[1]2023'!E26*100</f>
         <v>41.115520718712602</v>
       </c>
     </row>
-    <row r="47" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="13" t="s">
         <v>11</v>
       </c>
@@ -2681,19 +1713,16 @@
         <v>2022</v>
       </c>
       <c r="E47" s="15">
-        <f>'[1]2022'!D7/'[1]2022'!D24*100</f>
         <v>6.1678110089607818</v>
       </c>
       <c r="F47" s="15">
-        <f>'[1]2022'!F7/'[1]2022'!F24*100</f>
         <v>14.976041033947496</v>
       </c>
       <c r="G47" s="15">
-        <f>'[1]2022'!E7/'[1]2022'!E24*100</f>
         <v>2.6128136737248919</v>
       </c>
     </row>
-    <row r="48" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="13" t="s">
         <v>13</v>
       </c>
@@ -2704,19 +1733,16 @@
         <v>2022</v>
       </c>
       <c r="E48" s="15">
-        <f>'[1]2022'!D8/'[1]2022'!D25*100</f>
         <v>5.9559999576311577</v>
       </c>
       <c r="F48" s="15">
-        <f>'[1]2022'!F8/'[1]2022'!F25*100</f>
         <v>13.783955857385397</v>
       </c>
       <c r="G48" s="15">
-        <f>'[1]2022'!E8/'[1]2022'!E25*100</f>
         <v>2.6097343393259447</v>
       </c>
     </row>
-    <row r="49" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="13" t="s">
         <v>14</v>
       </c>
@@ -2727,19 +1753,16 @@
         <v>2022</v>
       </c>
       <c r="E49" s="15">
-        <f>'[1]2022'!D9/'[1]2022'!D26*100</f>
         <v>5.6222223156584663</v>
       </c>
       <c r="F49" s="15">
-        <f>'[1]2022'!F9/'[1]2022'!F26*100</f>
         <v>15.487924569453648</v>
       </c>
       <c r="G49" s="15">
-        <f>'[1]2022'!E9/'[1]2022'!E26*100</f>
         <v>2.3228673384653367</v>
       </c>
     </row>
-    <row r="50" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="13" t="s">
         <v>11</v>
       </c>
@@ -2750,19 +1773,16 @@
         <v>2022</v>
       </c>
       <c r="E50" s="15">
-        <f>'[1]2022'!D11/'[1]2022'!D24*100</f>
         <v>10.919740874355094</v>
       </c>
       <c r="F50" s="15">
-        <f>'[1]2022'!F11/'[1]2022'!F24*100</f>
         <v>15.644192481608965</v>
       </c>
       <c r="G50" s="15">
-        <f>'[1]2022'!E11/'[1]2022'!E24*100</f>
         <v>9.0142071743508794</v>
       </c>
     </row>
-    <row r="51" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="13" t="s">
         <v>13</v>
       </c>
@@ -2773,19 +1793,16 @@
         <v>2022</v>
       </c>
       <c r="E51" s="15">
-        <f>'[1]2022'!D12/'[1]2022'!D25*100</f>
         <v>10.458748636252899</v>
       </c>
       <c r="F51" s="15">
-        <f>'[1]2022'!F12/'[1]2022'!F25*100</f>
         <v>12.860780984719863</v>
       </c>
       <c r="G51" s="15">
-        <f>'[1]2022'!E12/'[1]2022'!E25*100</f>
         <v>9.4319367373784733</v>
       </c>
     </row>
-    <row r="52" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="13" t="s">
         <v>14</v>
       </c>
@@ -2796,19 +1813,16 @@
         <v>2022</v>
       </c>
       <c r="E52" s="15">
-        <f>'[1]2022'!D13/'[1]2022'!D26*100</f>
         <v>17.659870581458417</v>
       </c>
       <c r="F52" s="15">
-        <f>'[1]2022'!F13/'[1]2022'!F26*100</f>
         <v>17.331745086360932</v>
       </c>
       <c r="G52" s="15">
-        <f>'[1]2022'!E13/'[1]2022'!E26*100</f>
         <v>17.769654599726191</v>
       </c>
     </row>
-    <row r="53" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="13" t="s">
         <v>11</v>
       </c>
@@ -2819,19 +1833,16 @@
         <v>2022</v>
       </c>
       <c r="E53" s="15">
-        <f>'[1]2022'!D15/'[1]2022'!D24*100</f>
         <v>34.819038752472942</v>
       </c>
       <c r="F53" s="15">
-        <f>'[1]2022'!F15/'[1]2022'!F24*100</f>
         <v>30.518998447728961</v>
       </c>
       <c r="G53" s="15">
-        <f>'[1]2022'!E15/'[1]2022'!E24*100</f>
         <v>36.549452942137059</v>
       </c>
     </row>
-    <row r="54" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="13" t="s">
         <v>13</v>
       </c>
@@ -2842,19 +1853,16 @@
         <v>2022</v>
       </c>
       <c r="E54" s="15">
-        <f>'[1]2022'!D16/'[1]2022'!D25*100</f>
         <v>32.671673251490851</v>
       </c>
       <c r="F54" s="15">
-        <f>'[1]2022'!F16/'[1]2022'!F25*100</f>
         <v>25.014148273910582</v>
       </c>
       <c r="G54" s="15">
-        <f>'[1]2022'!E16/'[1]2022'!E25*100</f>
         <v>35.945083689916387</v>
       </c>
     </row>
-    <row r="55" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="13" t="s">
         <v>14</v>
       </c>
@@ -2865,19 +1873,16 @@
         <v>2022</v>
       </c>
       <c r="E55" s="15">
-        <f>'[1]2022'!D17/'[1]2022'!D26*100</f>
         <v>35.929833118196377</v>
       </c>
       <c r="F55" s="15">
-        <f>'[1]2022'!F17/'[1]2022'!F26*100</f>
         <v>29.55649321779396</v>
       </c>
       <c r="G55" s="15">
-        <f>'[1]2022'!E17/'[1]2022'!E26*100</f>
         <v>38.06135960679579</v>
       </c>
     </row>
-    <row r="56" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="13" t="s">
         <v>11</v>
       </c>
@@ -2888,19 +1893,16 @@
         <v>2022</v>
       </c>
       <c r="E56" s="15">
-        <f>'[1]2022'!D19/'[1]2022'!D24*100</f>
         <v>48.093409364211176</v>
       </c>
       <c r="F56" s="15">
-        <f>'[1]2022'!F19/'[1]2022'!F24*100</f>
         <v>38.854019032192753</v>
       </c>
       <c r="G56" s="15">
-        <f>'[1]2022'!E19/'[1]2022'!E24*100</f>
         <v>51.820804528877026</v>
       </c>
     </row>
-    <row r="57" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="13" t="s">
         <v>13</v>
       </c>
@@ -2911,19 +1913,16 @@
         <v>2022</v>
       </c>
       <c r="E57" s="15">
-        <f>'[1]2022'!D20/'[1]2022'!D25*100</f>
         <v>50.913578154625085</v>
       </c>
       <c r="F57" s="15">
-        <f>'[1]2022'!F20/'[1]2022'!F25*100</f>
         <v>48.34111488398414</v>
       </c>
       <c r="G57" s="15">
-        <f>'[1]2022'!E20/'[1]2022'!E25*100</f>
         <v>52.011733220436362</v>
       </c>
     </row>
-    <row r="58" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="13" t="s">
         <v>14</v>
       </c>
@@ -2934,19 +1933,16 @@
         <v>2022</v>
       </c>
       <c r="E58" s="15">
-        <f>'[1]2022'!D21/'[1]2022'!D26*100</f>
         <v>40.787863753137707</v>
       </c>
       <c r="F58" s="15">
-        <f>'[1]2022'!F21/'[1]2022'!F26*100</f>
         <v>37.623837126391464</v>
       </c>
       <c r="G58" s="15">
-        <f>'[1]2022'!E21/'[1]2022'!E26*100</f>
         <v>41.846118455012679</v>
       </c>
     </row>
-    <row r="59" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="13" t="s">
         <v>11</v>
       </c>
@@ -2957,19 +1953,16 @@
         <v>2021</v>
       </c>
       <c r="E59" s="15">
-        <f>'[1]2021'!D7/'[1]2021'!D24*100</f>
         <v>6.0801410796512201</v>
       </c>
       <c r="F59" s="15">
-        <f>'[1]2021'!F7/'[1]2021'!F24*100</f>
         <v>13.32275424313509</v>
       </c>
       <c r="G59" s="15">
-        <f>'[1]2021'!E7/'[1]2021'!E24*100</f>
         <v>3.2073561205221535</v>
       </c>
     </row>
-    <row r="60" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="13" t="s">
         <v>13</v>
       </c>
@@ -2980,19 +1973,16 @@
         <v>2021</v>
       </c>
       <c r="E60" s="15">
-        <f>'[1]2021'!D8/'[1]2021'!D25*100</f>
         <v>6.1689494780614327</v>
       </c>
       <c r="F60" s="15">
-        <f>'[1]2021'!F8/'[1]2021'!F25*100</f>
         <v>14.350864288341306</v>
       </c>
       <c r="G60" s="15">
-        <f>'[1]2021'!E8/'[1]2021'!E25*100</f>
         <v>2.8056324394633756</v>
       </c>
     </row>
-    <row r="61" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="13" t="s">
         <v>14</v>
       </c>
@@ -3003,19 +1993,16 @@
         <v>2021</v>
       </c>
       <c r="E61" s="15">
-        <f>'[1]2021'!D9/'[1]2021'!D26*100</f>
         <v>5.5177068478891007</v>
       </c>
       <c r="F61" s="15">
-        <f>'[1]2021'!F9/'[1]2021'!F26*100</f>
         <v>15.136402349614981</v>
       </c>
       <c r="G61" s="15">
-        <f>'[1]2021'!E9/'[1]2021'!E26*100</f>
         <v>2.4643833745411161</v>
       </c>
     </row>
-    <row r="62" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="13" t="s">
         <v>11</v>
       </c>
@@ -3026,19 +2013,16 @@
         <v>2021</v>
       </c>
       <c r="E62" s="15">
-        <f>'[1]2021'!D11/'[1]2021'!D24*100</f>
         <v>11.064955422749092</v>
       </c>
       <c r="F62" s="15">
-        <f>'[1]2021'!F11/'[1]2021'!F24*100</f>
         <v>14.419759900648543</v>
       </c>
       <c r="G62" s="15">
-        <f>'[1]2021'!E11/'[1]2021'!E24*100</f>
         <v>9.7342710927451357</v>
       </c>
     </row>
-    <row r="63" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="13" t="s">
         <v>13</v>
       </c>
@@ -3049,19 +2033,16 @@
         <v>2021</v>
       </c>
       <c r="E63" s="15">
-        <f>'[1]2021'!D12/'[1]2021'!D25*100</f>
         <v>10.703491736865796</v>
       </c>
       <c r="F63" s="15">
-        <f>'[1]2021'!F12/'[1]2021'!F25*100</f>
         <v>13.920559029054802</v>
       </c>
       <c r="G63" s="15">
-        <f>'[1]2021'!E12/'[1]2021'!E25*100</f>
         <v>9.3788284404918549</v>
       </c>
     </row>
-    <row r="64" spans="2:7" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="13" t="s">
         <v>14</v>
       </c>
@@ -3072,19 +2053,16 @@
         <v>2021</v>
       </c>
       <c r="E64" s="15">
-        <f>'[1]2021'!D13/'[1]2021'!D26*100</f>
         <v>18.788004451572228</v>
       </c>
       <c r="F64" s="15">
-        <f>'[1]2021'!F13/'[1]2021'!F26*100</f>
         <v>18.213028246305676</v>
       </c>
       <c r="G64" s="15">
-        <f>'[1]2021'!E13/'[1]2021'!E26*100</f>
         <v>18.970539454942287</v>
       </c>
     </row>
-    <row r="65" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="13" t="s">
         <v>11</v>
       </c>
@@ -3095,19 +2073,16 @@
         <v>2021</v>
       </c>
       <c r="E65" s="15">
-        <f>'[1]2021'!D15/'[1]2021'!D24*100</f>
         <v>35.056333888507886</v>
       </c>
       <c r="F65" s="15">
-        <f>'[1]2021'!F15/'[1]2021'!F24*100</f>
         <v>33.220643024699875</v>
       </c>
       <c r="G65" s="15">
-        <f>'[1]2021'!E15/'[1]2021'!E24*100</f>
         <v>35.784461290057742</v>
       </c>
     </row>
-    <row r="66" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="13" t="s">
         <v>13</v>
       </c>
@@ -3118,19 +2093,16 @@
         <v>2021</v>
       </c>
       <c r="E66" s="15">
-        <f>'[1]2021'!D16/'[1]2021'!D25*100</f>
         <v>32.942147343150495</v>
       </c>
       <c r="F66" s="15">
-        <f>'[1]2021'!F16/'[1]2021'!F25*100</f>
         <v>25.454211107024644</v>
       </c>
       <c r="G66" s="15">
-        <f>'[1]2021'!E16/'[1]2021'!E25*100</f>
         <v>36.022505558328419</v>
       </c>
     </row>
-    <row r="67" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="13" t="s">
         <v>14</v>
       </c>
@@ -3141,19 +2113,16 @@
         <v>2021</v>
       </c>
       <c r="E67" s="15">
-        <f>'[1]2021'!D17/'[1]2021'!D26*100</f>
         <v>36.048848811574089</v>
       </c>
       <c r="F67" s="15">
-        <f>'[1]2021'!F17/'[1]2021'!F26*100</f>
         <v>30.623139668630529</v>
       </c>
       <c r="G67" s="15">
-        <f>'[1]2021'!E17/'[1]2021'!E26*100</f>
         <v>37.77132328551</v>
       </c>
     </row>
-    <row r="68" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="13" t="s">
         <v>11</v>
       </c>
@@ -3164,19 +2133,16 @@
         <v>2021</v>
       </c>
       <c r="E68" s="15">
-        <f>'[1]2021'!D19/'[1]2021'!D24*100</f>
         <v>47.79661016949153</v>
       </c>
       <c r="F68" s="15">
-        <f>'[1]2021'!F19/'[1]2021'!F24*100</f>
         <v>39.029943424865458</v>
       </c>
       <c r="G68" s="15">
-        <f>'[1]2021'!E19/'[1]2021'!E24*100</f>
         <v>51.27391149667497</v>
       </c>
     </row>
-    <row r="69" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="13" t="s">
         <v>13</v>
       </c>
@@ -3187,19 +2153,16 @@
         <v>2021</v>
       </c>
       <c r="E69" s="15">
-        <f>'[1]2021'!D20/'[1]2021'!D25*100</f>
         <v>50.185411441922277</v>
       </c>
       <c r="F69" s="15">
-        <f>'[1]2021'!F20/'[1]2021'!F25*100</f>
         <v>46.27436557557926</v>
       </c>
       <c r="G69" s="15">
-        <f>'[1]2021'!E20/'[1]2021'!E25*100</f>
         <v>51.793033561716349</v>
       </c>
     </row>
-    <row r="70" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="13" t="s">
         <v>14</v>
       </c>
@@ -3210,19 +2173,16 @@
         <v>2021</v>
       </c>
       <c r="E70" s="15">
-        <f>'[1]2021'!D21/'[1]2021'!D26*100</f>
         <v>39.645228312337878</v>
       </c>
       <c r="F70" s="15">
-        <f>'[1]2021'!F21/'[1]2021'!F26*100</f>
         <v>36.027429735448798</v>
       </c>
       <c r="G70" s="15">
-        <f>'[1]2021'!E21/'[1]2021'!E26*100</f>
         <v>40.793753885006588</v>
       </c>
     </row>
-    <row r="71" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="13" t="s">
         <v>11</v>
       </c>
@@ -3241,11 +2201,11 @@
       <c r="G71" s="15">
         <v>2.3615485127004585</v>
       </c>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
-    </row>
-    <row r="72" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="23"/>
+      <c r="J71" s="23"/>
+      <c r="K71" s="23"/>
+    </row>
+    <row r="72" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="13" t="s">
         <v>13</v>
       </c>
@@ -3264,11 +2224,11 @@
       <c r="G72" s="15">
         <v>1.8385398544695397</v>
       </c>
-      <c r="I72" s="40"/>
-      <c r="J72" s="40"/>
-      <c r="K72" s="40"/>
-    </row>
-    <row r="73" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I72" s="23"/>
+      <c r="J72" s="23"/>
+      <c r="K72" s="23"/>
+    </row>
+    <row r="73" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="13" t="s">
         <v>14</v>
       </c>
@@ -3287,11 +2247,11 @@
       <c r="G73" s="15">
         <v>1.9346383338033166</v>
       </c>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-    </row>
-    <row r="74" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="23"/>
+      <c r="J73" s="23"/>
+      <c r="K73" s="23"/>
+    </row>
+    <row r="74" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="13" t="s">
         <v>11</v>
       </c>
@@ -3310,11 +2270,11 @@
       <c r="G74" s="15">
         <v>10.284271441944323</v>
       </c>
-      <c r="I74" s="40"/>
-      <c r="J74" s="40"/>
-      <c r="K74" s="40"/>
-    </row>
-    <row r="75" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="23"/>
+    </row>
+    <row r="75" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="13" t="s">
         <v>13</v>
       </c>
@@ -3333,11 +2293,11 @@
       <c r="G75" s="15">
         <v>12.04569535421993</v>
       </c>
-      <c r="I75" s="40"/>
-      <c r="J75" s="40"/>
-      <c r="K75" s="40"/>
-    </row>
-    <row r="76" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I75" s="23"/>
+      <c r="J75" s="23"/>
+      <c r="K75" s="23"/>
+    </row>
+    <row r="76" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="13" t="s">
         <v>14</v>
       </c>
@@ -3356,11 +2316,11 @@
       <c r="G76" s="15">
         <v>21.893700258293645</v>
       </c>
-      <c r="I76" s="40"/>
-      <c r="J76" s="40"/>
-      <c r="K76" s="40"/>
-    </row>
-    <row r="77" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="23"/>
+    </row>
+    <row r="77" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="13" t="s">
         <v>11</v>
       </c>
@@ -3379,11 +2339,11 @@
       <c r="G77" s="15">
         <v>35.877957534518096</v>
       </c>
-      <c r="I77" s="40"/>
-      <c r="J77" s="40"/>
-      <c r="K77" s="40"/>
-    </row>
-    <row r="78" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I77" s="23"/>
+      <c r="J77" s="23"/>
+      <c r="K77" s="23"/>
+    </row>
+    <row r="78" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="13" t="s">
         <v>13</v>
       </c>
@@ -3402,11 +2362,11 @@
       <c r="G78" s="15">
         <v>38.641993555511853</v>
       </c>
-      <c r="I78" s="40"/>
-      <c r="J78" s="40"/>
-      <c r="K78" s="40"/>
-    </row>
-    <row r="79" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
+      <c r="K78" s="23"/>
+    </row>
+    <row r="79" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="13" t="s">
         <v>14</v>
       </c>
@@ -3425,11 +2385,11 @@
       <c r="G79" s="15">
         <v>38.772982954836024</v>
       </c>
-      <c r="I79" s="40"/>
-      <c r="J79" s="40"/>
-      <c r="K79" s="40"/>
-    </row>
-    <row r="80" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I79" s="23"/>
+      <c r="J79" s="23"/>
+      <c r="K79" s="23"/>
+    </row>
+    <row r="80" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="13" t="s">
         <v>11</v>
       </c>
@@ -3448,11 +2408,11 @@
       <c r="G80" s="15">
         <v>51.476222510837118</v>
       </c>
-      <c r="I80" s="40"/>
-      <c r="J80" s="40"/>
-      <c r="K80" s="40"/>
-    </row>
-    <row r="81" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I80" s="23"/>
+      <c r="J80" s="23"/>
+      <c r="K80" s="23"/>
+    </row>
+    <row r="81" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="13" t="s">
         <v>13</v>
       </c>
@@ -3471,11 +2431,11 @@
       <c r="G81" s="15">
         <v>47.473771235798679</v>
       </c>
-      <c r="I81" s="40"/>
-      <c r="J81" s="40"/>
-      <c r="K81" s="40"/>
-    </row>
-    <row r="82" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I81" s="23"/>
+      <c r="J81" s="23"/>
+      <c r="K81" s="23"/>
+    </row>
+    <row r="82" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="13" t="s">
         <v>14</v>
       </c>
@@ -3494,11 +2454,11 @@
       <c r="G82" s="15">
         <v>37.398678453067021</v>
       </c>
-      <c r="I82" s="40"/>
-      <c r="J82" s="40"/>
-      <c r="K82" s="40"/>
-    </row>
-    <row r="83" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I82" s="23"/>
+      <c r="J82" s="23"/>
+      <c r="K82" s="23"/>
+    </row>
+    <row r="83" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="13" t="s">
         <v>11</v>
       </c>
@@ -3517,9 +2477,9 @@
       <c r="G83" s="17">
         <v>2.2291467436960244</v>
       </c>
-      <c r="K83" s="40"/>
-    </row>
-    <row r="84" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K83" s="23"/>
+    </row>
+    <row r="84" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="13" t="s">
         <v>13</v>
       </c>
@@ -3538,9 +2498,9 @@
       <c r="G84" s="17">
         <v>1.9928666094218581</v>
       </c>
-      <c r="K84" s="40"/>
-    </row>
-    <row r="85" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K84" s="23"/>
+    </row>
+    <row r="85" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="13" t="s">
         <v>14</v>
       </c>
@@ -3559,9 +2519,9 @@
       <c r="G85" s="17">
         <v>1.9130584896634324</v>
       </c>
-      <c r="K85" s="40"/>
-    </row>
-    <row r="86" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K85" s="23"/>
+    </row>
+    <row r="86" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="13" t="s">
         <v>11</v>
       </c>
@@ -3580,9 +2540,9 @@
       <c r="G86" s="17">
         <v>11.793569434524862</v>
       </c>
-      <c r="K86" s="40"/>
-    </row>
-    <row r="87" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K86" s="23"/>
+    </row>
+    <row r="87" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="13" t="s">
         <v>13</v>
       </c>
@@ -3601,9 +2561,9 @@
       <c r="G87" s="17">
         <v>13.1807434985902</v>
       </c>
-      <c r="K87" s="40"/>
-    </row>
-    <row r="88" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K87" s="23"/>
+    </row>
+    <row r="88" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="13" t="s">
         <v>14</v>
       </c>
@@ -3622,9 +2582,9 @@
       <c r="G88" s="17">
         <v>23.368174845770174</v>
       </c>
-      <c r="K88" s="40"/>
-    </row>
-    <row r="89" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K88" s="23"/>
+    </row>
+    <row r="89" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="13" t="s">
         <v>11</v>
       </c>
@@ -3643,9 +2603,9 @@
       <c r="G89" s="17">
         <v>36.212795946112124</v>
       </c>
-      <c r="K89" s="40"/>
-    </row>
-    <row r="90" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K89" s="23"/>
+    </row>
+    <row r="90" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="13" t="s">
         <v>13</v>
       </c>
@@ -3664,9 +2624,9 @@
       <c r="G90" s="17">
         <v>39.324606196280122</v>
       </c>
-      <c r="K90" s="40"/>
-    </row>
-    <row r="91" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K90" s="23"/>
+    </row>
+    <row r="91" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="13" t="s">
         <v>14</v>
       </c>
@@ -3685,9 +2645,9 @@
       <c r="G91" s="17">
         <v>38.73613337230266</v>
       </c>
-      <c r="K91" s="40"/>
-    </row>
-    <row r="92" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K91" s="23"/>
+    </row>
+    <row r="92" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="13" t="s">
         <v>11</v>
       </c>
@@ -3706,9 +2666,9 @@
       <c r="G92" s="17">
         <v>49.764487875666994</v>
       </c>
-      <c r="K92" s="40"/>
-    </row>
-    <row r="93" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K92" s="23"/>
+    </row>
+    <row r="93" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="13" t="s">
         <v>13</v>
       </c>
@@ -3727,9 +2687,9 @@
       <c r="G93" s="17">
         <v>45.501782182389192</v>
       </c>
-      <c r="K93" s="40"/>
-    </row>
-    <row r="94" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K93" s="23"/>
+    </row>
+    <row r="94" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="13" t="s">
         <v>14</v>
       </c>
@@ -3748,9 +2708,9 @@
       <c r="G94" s="17">
         <v>35.982633292263735</v>
       </c>
-      <c r="K94" s="40"/>
-    </row>
-    <row r="95" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K94" s="23"/>
+    </row>
+    <row r="95" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="13" t="s">
         <v>11</v>
       </c>
@@ -3769,12 +2729,12 @@
       <c r="G95" s="18">
         <v>2.3349766564321568</v>
       </c>
-      <c r="H95" s="40"/>
-      <c r="I95" s="40"/>
-      <c r="J95" s="40"/>
-      <c r="K95" s="40"/>
-    </row>
-    <row r="96" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H95" s="23"/>
+      <c r="I95" s="23"/>
+      <c r="J95" s="23"/>
+      <c r="K95" s="23"/>
+    </row>
+    <row r="96" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="13" t="s">
         <v>13</v>
       </c>
@@ -3793,12 +2753,12 @@
       <c r="G96" s="18">
         <v>2.190582010262685</v>
       </c>
-      <c r="H96" s="40"/>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40"/>
-      <c r="K96" s="40"/>
-    </row>
-    <row r="97" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H96" s="23"/>
+      <c r="I96" s="23"/>
+      <c r="J96" s="23"/>
+      <c r="K96" s="23"/>
+    </row>
+    <row r="97" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="13" t="s">
         <v>14</v>
       </c>
@@ -3817,12 +2777,12 @@
       <c r="G97" s="18">
         <v>1.994779674772662</v>
       </c>
-      <c r="H97" s="40"/>
-      <c r="I97" s="40"/>
-      <c r="J97" s="40"/>
-      <c r="K97" s="40"/>
-    </row>
-    <row r="98" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H97" s="23"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="23"/>
+      <c r="K97" s="23"/>
+    </row>
+    <row r="98" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="13" t="s">
         <v>11</v>
       </c>
@@ -3841,12 +2801,12 @@
       <c r="G98" s="18">
         <v>11.39255908457678</v>
       </c>
-      <c r="H98" s="40"/>
-      <c r="I98" s="40"/>
-      <c r="J98" s="40"/>
-      <c r="K98" s="40"/>
-    </row>
-    <row r="99" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H98" s="23"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="23"/>
+      <c r="K98" s="23"/>
+    </row>
+    <row r="99" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="13" t="s">
         <v>13</v>
       </c>
@@ -3865,12 +2825,12 @@
       <c r="G99" s="18">
         <v>12.738203781254084</v>
       </c>
-      <c r="H99" s="40"/>
-      <c r="I99" s="40"/>
-      <c r="J99" s="40"/>
-      <c r="K99" s="40"/>
-    </row>
-    <row r="100" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H99" s="23"/>
+      <c r="I99" s="23"/>
+      <c r="J99" s="23"/>
+      <c r="K99" s="23"/>
+    </row>
+    <row r="100" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="13" t="s">
         <v>14</v>
       </c>
@@ -3889,12 +2849,12 @@
       <c r="G100" s="18">
         <v>24.606683498434101</v>
       </c>
-      <c r="H100" s="40"/>
-      <c r="I100" s="40"/>
-      <c r="J100" s="40"/>
-      <c r="K100" s="40"/>
-    </row>
-    <row r="101" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H100" s="23"/>
+      <c r="I100" s="23"/>
+      <c r="J100" s="23"/>
+      <c r="K100" s="23"/>
+    </row>
+    <row r="101" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="13" t="s">
         <v>11</v>
       </c>
@@ -3913,12 +2873,12 @@
       <c r="G101" s="18">
         <v>38.380235070800403</v>
       </c>
-      <c r="H101" s="40"/>
-      <c r="I101" s="40"/>
-      <c r="J101" s="40"/>
-      <c r="K101" s="40"/>
-    </row>
-    <row r="102" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H101" s="23"/>
+      <c r="I101" s="23"/>
+      <c r="J101" s="23"/>
+      <c r="K101" s="23"/>
+    </row>
+    <row r="102" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="13" t="s">
         <v>13</v>
       </c>
@@ -3937,12 +2897,12 @@
       <c r="G102" s="18">
         <v>39.398621285002122</v>
       </c>
-      <c r="H102" s="40"/>
-      <c r="I102" s="40"/>
-      <c r="J102" s="40"/>
-      <c r="K102" s="40"/>
-    </row>
-    <row r="103" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+    </row>
+    <row r="103" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="13" t="s">
         <v>14</v>
       </c>
@@ -3961,12 +2921,12 @@
       <c r="G103" s="18">
         <v>38.196210903481202</v>
       </c>
-      <c r="H103" s="40"/>
-      <c r="I103" s="40"/>
-      <c r="J103" s="40"/>
-      <c r="K103" s="40"/>
-    </row>
-    <row r="104" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H103" s="23"/>
+      <c r="I103" s="23"/>
+      <c r="J103" s="23"/>
+      <c r="K103" s="23"/>
+    </row>
+    <row r="104" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="13" t="s">
         <v>11</v>
       </c>
@@ -3985,12 +2945,12 @@
       <c r="G104" s="18">
         <v>47.892229188190669</v>
       </c>
-      <c r="H104" s="40"/>
-      <c r="I104" s="40"/>
-      <c r="J104" s="40"/>
-      <c r="K104" s="40"/>
-    </row>
-    <row r="105" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H104" s="23"/>
+      <c r="I104" s="23"/>
+      <c r="J104" s="23"/>
+      <c r="K104" s="23"/>
+    </row>
+    <row r="105" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="13" t="s">
         <v>13</v>
       </c>
@@ -4009,12 +2969,12 @@
       <c r="G105" s="18">
         <v>45.672594439875638</v>
       </c>
-      <c r="H105" s="40"/>
-      <c r="I105" s="40"/>
-      <c r="J105" s="40"/>
-      <c r="K105" s="40"/>
-    </row>
-    <row r="106" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H105" s="23"/>
+      <c r="I105" s="23"/>
+      <c r="J105" s="23"/>
+      <c r="K105" s="23"/>
+    </row>
+    <row r="106" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="13" t="s">
         <v>14</v>
       </c>
@@ -4033,12 +2993,12 @@
       <c r="G106" s="18">
         <v>35.202325923312038</v>
       </c>
-      <c r="H106" s="40"/>
-      <c r="I106" s="40"/>
-      <c r="J106" s="40"/>
-      <c r="K106" s="40"/>
-    </row>
-    <row r="107" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H106" s="23"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="23"/>
+      <c r="K106" s="23"/>
+    </row>
+    <row r="107" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="13" t="s">
         <v>11</v>
       </c>
@@ -4057,12 +3017,12 @@
       <c r="G107" s="19">
         <v>2.8693745396851096</v>
       </c>
-      <c r="H107" s="40"/>
-      <c r="I107" s="40"/>
-      <c r="J107" s="40"/>
-      <c r="K107" s="40"/>
-    </row>
-    <row r="108" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="23"/>
+      <c r="K107" s="23"/>
+    </row>
+    <row r="108" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="13" t="s">
         <v>13</v>
       </c>
@@ -4081,12 +3041,12 @@
       <c r="G108" s="19">
         <v>2.2480152377796392</v>
       </c>
-      <c r="H108" s="40"/>
-      <c r="I108" s="40"/>
-      <c r="J108" s="40"/>
-      <c r="K108" s="40"/>
-    </row>
-    <row r="109" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+    </row>
+    <row r="109" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="13" t="s">
         <v>14</v>
       </c>
@@ -4105,12 +3065,12 @@
       <c r="G109" s="19">
         <v>2.1814518113725949</v>
       </c>
-      <c r="H109" s="40"/>
-      <c r="I109" s="40"/>
-      <c r="J109" s="40"/>
-      <c r="K109" s="40"/>
-    </row>
-    <row r="110" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H109" s="23"/>
+      <c r="I109" s="23"/>
+      <c r="J109" s="23"/>
+      <c r="K109" s="23"/>
+    </row>
+    <row r="110" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="13" t="s">
         <v>11</v>
       </c>
@@ -4129,12 +3089,12 @@
       <c r="G110" s="19">
         <v>12.183810954144603</v>
       </c>
-      <c r="H110" s="40"/>
-      <c r="I110" s="40"/>
-      <c r="J110" s="40"/>
-      <c r="K110" s="40"/>
-    </row>
-    <row r="111" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H110" s="23"/>
+      <c r="I110" s="23"/>
+      <c r="J110" s="23"/>
+      <c r="K110" s="23"/>
+    </row>
+    <row r="111" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="13" t="s">
         <v>13</v>
       </c>
@@ -4153,12 +3113,12 @@
       <c r="G111" s="19">
         <v>13.709942976140971</v>
       </c>
-      <c r="H111" s="40"/>
-      <c r="I111" s="40"/>
-      <c r="J111" s="40"/>
-      <c r="K111" s="40"/>
-    </row>
-    <row r="112" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H111" s="23"/>
+      <c r="I111" s="23"/>
+      <c r="J111" s="23"/>
+      <c r="K111" s="23"/>
+    </row>
+    <row r="112" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="13" t="s">
         <v>14</v>
       </c>
@@ -4177,12 +3137,12 @@
       <c r="G112" s="19">
         <v>25.751162968500303</v>
       </c>
-      <c r="H112" s="40"/>
-      <c r="I112" s="40"/>
-      <c r="J112" s="40"/>
-      <c r="K112" s="40"/>
-    </row>
-    <row r="113" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="23"/>
+      <c r="K112" s="23"/>
+    </row>
+    <row r="113" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="13" t="s">
         <v>11</v>
       </c>
@@ -4201,12 +3161,12 @@
       <c r="G113" s="19">
         <v>39.106860255633862</v>
       </c>
-      <c r="H113" s="40"/>
-      <c r="I113" s="40"/>
-      <c r="J113" s="40"/>
-      <c r="K113" s="40"/>
-    </row>
-    <row r="114" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H113" s="23"/>
+      <c r="I113" s="23"/>
+      <c r="J113" s="23"/>
+      <c r="K113" s="23"/>
+    </row>
+    <row r="114" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="13" t="s">
         <v>13</v>
       </c>
@@ -4225,12 +3185,12 @@
       <c r="G114" s="19">
         <v>38.879705125856184</v>
       </c>
-      <c r="H114" s="40"/>
-      <c r="I114" s="40"/>
-      <c r="J114" s="40"/>
-      <c r="K114" s="40"/>
-    </row>
-    <row r="115" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H114" s="23"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23"/>
+      <c r="K114" s="23"/>
+    </row>
+    <row r="115" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="13" t="s">
         <v>14</v>
       </c>
@@ -4249,12 +3209,12 @@
       <c r="G115" s="19">
         <v>37.880958310287554</v>
       </c>
-      <c r="H115" s="40"/>
-      <c r="I115" s="40"/>
-      <c r="J115" s="40"/>
-      <c r="K115" s="40"/>
-    </row>
-    <row r="116" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H115" s="23"/>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="23"/>
+    </row>
+    <row r="116" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="13" t="s">
         <v>11</v>
       </c>
@@ -4273,12 +3233,12 @@
       <c r="G116" s="19">
         <v>45.839954250536422</v>
       </c>
-      <c r="H116" s="40"/>
-      <c r="I116" s="40"/>
-      <c r="J116" s="40"/>
-      <c r="K116" s="40"/>
-    </row>
-    <row r="117" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H116" s="23"/>
+      <c r="I116" s="23"/>
+      <c r="J116" s="23"/>
+      <c r="K116" s="23"/>
+    </row>
+    <row r="117" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="13" t="s">
         <v>13</v>
       </c>
@@ -4297,12 +3257,12 @@
       <c r="G117" s="19">
         <v>45.162338100499696</v>
       </c>
-      <c r="H117" s="40"/>
-      <c r="I117" s="40"/>
-      <c r="J117" s="40"/>
-      <c r="K117" s="40"/>
-    </row>
-    <row r="118" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H117" s="23"/>
+      <c r="I117" s="23"/>
+      <c r="J117" s="23"/>
+      <c r="K117" s="23"/>
+    </row>
+    <row r="118" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="13" t="s">
         <v>14</v>
       </c>
@@ -4321,12 +3281,12 @@
       <c r="G118" s="19">
         <v>34.186427165516669</v>
       </c>
-      <c r="H118" s="40"/>
-      <c r="I118" s="40"/>
-      <c r="J118" s="40"/>
-      <c r="K118" s="40"/>
-    </row>
-    <row r="119" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="23"/>
+      <c r="K118" s="23"/>
+    </row>
+    <row r="119" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="13" t="s">
         <v>11</v>
       </c>
@@ -4345,12 +3305,12 @@
       <c r="G119" s="19">
         <v>2.8827232317372364</v>
       </c>
-      <c r="H119" s="40"/>
-      <c r="I119" s="40"/>
-      <c r="J119" s="40"/>
-      <c r="K119" s="40"/>
-    </row>
-    <row r="120" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H119" s="23"/>
+      <c r="I119" s="23"/>
+      <c r="J119" s="23"/>
+      <c r="K119" s="23"/>
+    </row>
+    <row r="120" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="13" t="s">
         <v>13</v>
       </c>
@@ -4369,12 +3329,12 @@
       <c r="G120" s="19">
         <v>2.6404567264316414</v>
       </c>
-      <c r="H120" s="40"/>
-      <c r="I120" s="40"/>
-      <c r="J120" s="40"/>
-      <c r="K120" s="40"/>
-    </row>
-    <row r="121" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H120" s="23"/>
+      <c r="I120" s="23"/>
+      <c r="J120" s="23"/>
+      <c r="K120" s="23"/>
+    </row>
+    <row r="121" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="13" t="s">
         <v>14</v>
       </c>
@@ -4393,12 +3353,12 @@
       <c r="G121" s="19">
         <v>2.121669380202122</v>
       </c>
-      <c r="H121" s="40"/>
-      <c r="I121" s="40"/>
-      <c r="J121" s="40"/>
-      <c r="K121" s="40"/>
-    </row>
-    <row r="122" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H121" s="23"/>
+      <c r="I121" s="23"/>
+      <c r="J121" s="23"/>
+      <c r="K121" s="23"/>
+    </row>
+    <row r="122" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="13" t="s">
         <v>11</v>
       </c>
@@ -4417,12 +3377,12 @@
       <c r="G122" s="19">
         <v>12.036645441407863</v>
       </c>
-      <c r="H122" s="40"/>
-      <c r="I122" s="40"/>
-      <c r="J122" s="40"/>
-      <c r="K122" s="40"/>
-    </row>
-    <row r="123" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H122" s="23"/>
+      <c r="I122" s="23"/>
+      <c r="J122" s="23"/>
+      <c r="K122" s="23"/>
+    </row>
+    <row r="123" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="13" t="s">
         <v>13</v>
       </c>
@@ -4441,12 +3401,12 @@
       <c r="G123" s="19">
         <v>13.054177914658844</v>
       </c>
-      <c r="H123" s="40"/>
-      <c r="I123" s="40"/>
-      <c r="J123" s="40"/>
-      <c r="K123" s="40"/>
-    </row>
-    <row r="124" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H123" s="23"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="23"/>
+      <c r="K123" s="23"/>
+    </row>
+    <row r="124" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="13" t="s">
         <v>14</v>
       </c>
@@ -4465,12 +3425,12 @@
       <c r="G124" s="19">
         <v>25.976715362649799</v>
       </c>
-      <c r="H124" s="40"/>
-      <c r="I124" s="40"/>
-      <c r="J124" s="40"/>
-      <c r="K124" s="40"/>
-    </row>
-    <row r="125" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H124" s="23"/>
+      <c r="I124" s="23"/>
+      <c r="J124" s="23"/>
+      <c r="K124" s="23"/>
+    </row>
+    <row r="125" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="13" t="s">
         <v>11</v>
       </c>
@@ -4489,12 +3449,12 @@
       <c r="G125" s="19">
         <v>40.266189611854642</v>
       </c>
-      <c r="H125" s="40"/>
-      <c r="I125" s="40"/>
-      <c r="J125" s="40"/>
-      <c r="K125" s="40"/>
-    </row>
-    <row r="126" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H125" s="23"/>
+      <c r="I125" s="23"/>
+      <c r="J125" s="23"/>
+      <c r="K125" s="23"/>
+    </row>
+    <row r="126" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="13" t="s">
         <v>13</v>
       </c>
@@ -4513,12 +3473,12 @@
       <c r="G126" s="19">
         <v>38.809618861549488</v>
       </c>
-      <c r="H126" s="40"/>
-      <c r="I126" s="40"/>
-      <c r="J126" s="40"/>
-      <c r="K126" s="40"/>
-    </row>
-    <row r="127" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H126" s="23"/>
+      <c r="I126" s="23"/>
+      <c r="J126" s="23"/>
+      <c r="K126" s="23"/>
+    </row>
+    <row r="127" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="13" t="s">
         <v>14</v>
       </c>
@@ -4537,12 +3497,12 @@
       <c r="G127" s="19">
         <v>38.055255437344449</v>
       </c>
-      <c r="H127" s="40"/>
-      <c r="I127" s="40"/>
-      <c r="J127" s="40"/>
-      <c r="K127" s="40"/>
-    </row>
-    <row r="128" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H127" s="23"/>
+      <c r="I127" s="23"/>
+      <c r="J127" s="23"/>
+      <c r="K127" s="23"/>
+    </row>
+    <row r="128" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="13" t="s">
         <v>11</v>
       </c>
@@ -4561,12 +3521,12 @@
       <c r="G128" s="19">
         <v>44.81443929372999</v>
       </c>
-      <c r="H128" s="40"/>
-      <c r="I128" s="40"/>
-      <c r="J128" s="40"/>
-      <c r="K128" s="40"/>
-    </row>
-    <row r="129" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H128" s="23"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="23"/>
+      <c r="K128" s="23"/>
+    </row>
+    <row r="129" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="13" t="s">
         <v>13</v>
       </c>
@@ -4585,12 +3545,12 @@
       <c r="G129" s="19">
         <v>45.495746497360031</v>
       </c>
-      <c r="H129" s="40"/>
-      <c r="I129" s="40"/>
-      <c r="J129" s="40"/>
-      <c r="K129" s="40"/>
-    </row>
-    <row r="130" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H129" s="23"/>
+      <c r="I129" s="23"/>
+      <c r="J129" s="23"/>
+      <c r="K129" s="23"/>
+    </row>
+    <row r="130" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="13" t="s">
         <v>14</v>
       </c>
@@ -4609,12 +3569,12 @@
       <c r="G130" s="19">
         <v>33.846359819803624</v>
       </c>
-      <c r="H130" s="40"/>
-      <c r="I130" s="40"/>
-      <c r="J130" s="40"/>
-      <c r="K130" s="40"/>
-    </row>
-    <row r="131" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H130" s="23"/>
+      <c r="I130" s="23"/>
+      <c r="J130" s="23"/>
+      <c r="K130" s="23"/>
+    </row>
+    <row r="131" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="13" t="s">
         <v>11</v>
       </c>
@@ -4633,12 +3593,12 @@
       <c r="G131" s="19">
         <v>3.4942196150433125</v>
       </c>
-      <c r="H131" s="40"/>
-      <c r="I131" s="40"/>
-      <c r="J131" s="40"/>
-      <c r="K131" s="40"/>
-    </row>
-    <row r="132" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H131" s="23"/>
+      <c r="I131" s="23"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="23"/>
+    </row>
+    <row r="132" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="13" t="s">
         <v>13</v>
       </c>
@@ -4657,12 +3617,12 @@
       <c r="G132" s="19">
         <v>2.4151845086418589</v>
       </c>
-      <c r="H132" s="40"/>
-      <c r="I132" s="40"/>
-      <c r="J132" s="40"/>
-      <c r="K132" s="40"/>
-    </row>
-    <row r="133" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H132" s="23"/>
+      <c r="I132" s="23"/>
+      <c r="J132" s="23"/>
+      <c r="K132" s="23"/>
+    </row>
+    <row r="133" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="13" t="s">
         <v>14</v>
       </c>
@@ -4681,12 +3641,12 @@
       <c r="G133" s="19">
         <v>2.2894831864733827</v>
       </c>
-      <c r="H133" s="40"/>
-      <c r="I133" s="40"/>
-      <c r="J133" s="40"/>
-      <c r="K133" s="40"/>
-    </row>
-    <row r="134" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H133" s="23"/>
+      <c r="I133" s="23"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="23"/>
+    </row>
+    <row r="134" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="13" t="s">
         <v>11</v>
       </c>
@@ -4705,12 +3665,12 @@
       <c r="G134" s="19">
         <v>13.065419033503062</v>
       </c>
-      <c r="H134" s="40"/>
-      <c r="I134" s="40"/>
-      <c r="J134" s="40"/>
-      <c r="K134" s="40"/>
-    </row>
-    <row r="135" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H134" s="23"/>
+      <c r="I134" s="23"/>
+      <c r="J134" s="23"/>
+      <c r="K134" s="23"/>
+    </row>
+    <row r="135" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="13" t="s">
         <v>13</v>
       </c>
@@ -4729,12 +3689,12 @@
       <c r="G135" s="19">
         <v>14.129317506186712</v>
       </c>
-      <c r="H135" s="40"/>
-      <c r="I135" s="40"/>
-      <c r="J135" s="40"/>
-      <c r="K135" s="40"/>
-    </row>
-    <row r="136" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H135" s="23"/>
+      <c r="I135" s="23"/>
+      <c r="J135" s="23"/>
+      <c r="K135" s="23"/>
+    </row>
+    <row r="136" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="13" t="s">
         <v>14</v>
       </c>
@@ -4753,12 +3713,12 @@
       <c r="G136" s="19">
         <v>27.428846216198711</v>
       </c>
-      <c r="H136" s="40"/>
-      <c r="I136" s="40"/>
-      <c r="J136" s="40"/>
-      <c r="K136" s="40"/>
-    </row>
-    <row r="137" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H136" s="23"/>
+      <c r="I136" s="23"/>
+      <c r="J136" s="23"/>
+      <c r="K136" s="23"/>
+    </row>
+    <row r="137" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B137" s="13" t="s">
         <v>11</v>
       </c>
@@ -4777,12 +3737,12 @@
       <c r="G137" s="19">
         <v>40.942167361311874</v>
       </c>
-      <c r="H137" s="40"/>
-      <c r="I137" s="40"/>
-      <c r="J137" s="40"/>
-      <c r="K137" s="40"/>
-    </row>
-    <row r="138" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="23"/>
+      <c r="K137" s="23"/>
+    </row>
+    <row r="138" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B138" s="13" t="s">
         <v>13</v>
       </c>
@@ -4801,12 +3761,12 @@
       <c r="G138" s="19">
         <v>40.470856654677874</v>
       </c>
-      <c r="H138" s="40"/>
-      <c r="I138" s="40"/>
-      <c r="J138" s="40"/>
-      <c r="K138" s="40"/>
-    </row>
-    <row r="139" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H138" s="23"/>
+      <c r="I138" s="23"/>
+      <c r="J138" s="23"/>
+      <c r="K138" s="23"/>
+    </row>
+    <row r="139" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="13" t="s">
         <v>14</v>
       </c>
@@ -4825,12 +3785,12 @@
       <c r="G139" s="19">
         <v>37.718834126586046</v>
       </c>
-      <c r="H139" s="40"/>
-      <c r="I139" s="40"/>
-      <c r="J139" s="40"/>
-      <c r="K139" s="40"/>
-    </row>
-    <row r="140" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H139" s="23"/>
+      <c r="I139" s="23"/>
+      <c r="J139" s="23"/>
+      <c r="K139" s="23"/>
+    </row>
+    <row r="140" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B140" s="13" t="s">
         <v>11</v>
       </c>
@@ -4849,12 +3809,12 @@
       <c r="G140" s="19">
         <v>42.49819399014175</v>
       </c>
-      <c r="H140" s="40"/>
-      <c r="I140" s="40"/>
-      <c r="J140" s="40"/>
-      <c r="K140" s="40"/>
-    </row>
-    <row r="141" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H140" s="23"/>
+      <c r="I140" s="23"/>
+      <c r="J140" s="23"/>
+      <c r="K140" s="23"/>
+    </row>
+    <row r="141" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="13" t="s">
         <v>13</v>
       </c>
@@ -4873,12 +3833,12 @@
       <c r="G141" s="19">
         <v>42.98464133049356</v>
       </c>
-      <c r="H141" s="40"/>
-      <c r="I141" s="40"/>
-      <c r="J141" s="40"/>
-      <c r="K141" s="40"/>
-    </row>
-    <row r="142" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H141" s="23"/>
+      <c r="I141" s="23"/>
+      <c r="J141" s="23"/>
+      <c r="K141" s="23"/>
+    </row>
+    <row r="142" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B142" s="13" t="s">
         <v>14</v>
       </c>
@@ -4897,12 +3857,12 @@
       <c r="G142" s="19">
         <v>32.562836726184457</v>
       </c>
-      <c r="H142" s="40"/>
-      <c r="I142" s="40"/>
-      <c r="J142" s="40"/>
-      <c r="K142" s="40"/>
-    </row>
-    <row r="143" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H142" s="23"/>
+      <c r="I142" s="23"/>
+      <c r="J142" s="23"/>
+      <c r="K142" s="23"/>
+    </row>
+    <row r="143" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="13" t="s">
         <v>11</v>
       </c>
@@ -4921,12 +3881,12 @@
       <c r="G143" s="19">
         <v>3.8581134596894184</v>
       </c>
-      <c r="H143" s="40"/>
-      <c r="I143" s="40"/>
-      <c r="J143" s="40"/>
-      <c r="K143" s="40"/>
-    </row>
-    <row r="144" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H143" s="23"/>
+      <c r="I143" s="23"/>
+      <c r="J143" s="23"/>
+      <c r="K143" s="23"/>
+    </row>
+    <row r="144" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="13" t="s">
         <v>13</v>
       </c>
@@ -4945,12 +3905,12 @@
       <c r="G144" s="19">
         <v>2.636205797609152</v>
       </c>
-      <c r="H144" s="40"/>
-      <c r="I144" s="40"/>
-      <c r="J144" s="40"/>
-      <c r="K144" s="40"/>
-    </row>
-    <row r="145" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H144" s="23"/>
+      <c r="I144" s="23"/>
+      <c r="J144" s="23"/>
+      <c r="K144" s="23"/>
+    </row>
+    <row r="145" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="13" t="s">
         <v>14</v>
       </c>
@@ -4969,12 +3929,12 @@
       <c r="G145" s="19">
         <v>2.2326660215626659</v>
       </c>
-      <c r="H145" s="40"/>
-      <c r="I145" s="40"/>
-      <c r="J145" s="40"/>
-      <c r="K145" s="40"/>
-    </row>
-    <row r="146" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H145" s="23"/>
+      <c r="I145" s="23"/>
+      <c r="J145" s="23"/>
+      <c r="K145" s="23"/>
+    </row>
+    <row r="146" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="13" t="s">
         <v>11</v>
       </c>
@@ -4993,12 +3953,12 @@
       <c r="G146" s="19">
         <v>13.882857065915472</v>
       </c>
-      <c r="H146" s="40"/>
-      <c r="I146" s="40"/>
-      <c r="J146" s="40"/>
-      <c r="K146" s="40"/>
-    </row>
-    <row r="147" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H146" s="23"/>
+      <c r="I146" s="23"/>
+      <c r="J146" s="23"/>
+      <c r="K146" s="23"/>
+    </row>
+    <row r="147" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="13" t="s">
         <v>13</v>
       </c>
@@ -5017,12 +3977,12 @@
       <c r="G147" s="19">
         <v>14.452252044901693</v>
       </c>
-      <c r="H147" s="40"/>
-      <c r="I147" s="40"/>
-      <c r="J147" s="40"/>
-      <c r="K147" s="40"/>
-    </row>
-    <row r="148" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H147" s="23"/>
+      <c r="I147" s="23"/>
+      <c r="J147" s="23"/>
+      <c r="K147" s="23"/>
+    </row>
+    <row r="148" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="13" t="s">
         <v>14</v>
       </c>
@@ -5041,12 +4001,12 @@
       <c r="G148" s="19">
         <v>28.642493790953527</v>
       </c>
-      <c r="H148" s="40"/>
-      <c r="I148" s="40"/>
-      <c r="J148" s="40"/>
-      <c r="K148" s="40"/>
-    </row>
-    <row r="149" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H148" s="23"/>
+      <c r="I148" s="23"/>
+      <c r="J148" s="23"/>
+      <c r="K148" s="23"/>
+    </row>
+    <row r="149" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B149" s="13" t="s">
         <v>11</v>
       </c>
@@ -5065,12 +4025,12 @@
       <c r="G149" s="19">
         <v>40.41508687096691</v>
       </c>
-      <c r="H149" s="40"/>
-      <c r="I149" s="40"/>
-      <c r="J149" s="40"/>
-      <c r="K149" s="40"/>
-    </row>
-    <row r="150" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H149" s="23"/>
+      <c r="I149" s="23"/>
+      <c r="J149" s="23"/>
+      <c r="K149" s="23"/>
+    </row>
+    <row r="150" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B150" s="13" t="s">
         <v>13</v>
       </c>
@@ -5089,12 +4049,12 @@
       <c r="G150" s="19">
         <v>40.693864658911529</v>
       </c>
-      <c r="H150" s="40"/>
-      <c r="I150" s="40"/>
-      <c r="J150" s="40"/>
-      <c r="K150" s="40"/>
-    </row>
-    <row r="151" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H150" s="23"/>
+      <c r="I150" s="23"/>
+      <c r="J150" s="23"/>
+      <c r="K150" s="23"/>
+    </row>
+    <row r="151" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="13" t="s">
         <v>14</v>
       </c>
@@ -5113,12 +4073,12 @@
       <c r="G151" s="19">
         <v>36.87476979632379</v>
       </c>
-      <c r="H151" s="40"/>
-      <c r="I151" s="40"/>
-      <c r="J151" s="40"/>
-      <c r="K151" s="40"/>
-    </row>
-    <row r="152" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H151" s="23"/>
+      <c r="I151" s="23"/>
+      <c r="J151" s="23"/>
+      <c r="K151" s="23"/>
+    </row>
+    <row r="152" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B152" s="13" t="s">
         <v>11</v>
       </c>
@@ -5137,12 +4097,12 @@
       <c r="G152" s="19">
         <v>41.843944980267125</v>
       </c>
-      <c r="H152" s="40"/>
-      <c r="I152" s="40"/>
-      <c r="J152" s="40"/>
-      <c r="K152" s="40"/>
-    </row>
-    <row r="153" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H152" s="23"/>
+      <c r="I152" s="23"/>
+      <c r="J152" s="23"/>
+      <c r="K152" s="23"/>
+    </row>
+    <row r="153" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B153" s="13" t="s">
         <v>13</v>
       </c>
@@ -5161,12 +4121,12 @@
       <c r="G153" s="19">
         <v>42.217676005589034</v>
       </c>
-      <c r="H153" s="40"/>
-      <c r="I153" s="40"/>
-      <c r="J153" s="40"/>
-      <c r="K153" s="40"/>
-    </row>
-    <row r="154" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H153" s="23"/>
+      <c r="I153" s="23"/>
+      <c r="J153" s="23"/>
+      <c r="K153" s="23"/>
+    </row>
+    <row r="154" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B154" s="13" t="s">
         <v>14</v>
       </c>
@@ -5185,12 +4145,12 @@
       <c r="G154" s="19">
         <v>32.250070647032501</v>
       </c>
-      <c r="H154" s="40"/>
-      <c r="I154" s="40"/>
-      <c r="J154" s="40"/>
-      <c r="K154" s="40"/>
-    </row>
-    <row r="155" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H154" s="23"/>
+      <c r="I154" s="23"/>
+      <c r="J154" s="23"/>
+      <c r="K154" s="23"/>
+    </row>
+    <row r="155" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B155" s="13" t="s">
         <v>11</v>
       </c>
@@ -5209,12 +4169,12 @@
       <c r="G155" s="19">
         <v>4.4659382405956984</v>
       </c>
-      <c r="H155" s="40"/>
-      <c r="I155" s="40"/>
-      <c r="J155" s="40"/>
-      <c r="K155" s="40"/>
-    </row>
-    <row r="156" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H155" s="23"/>
+      <c r="I155" s="23"/>
+      <c r="J155" s="23"/>
+      <c r="K155" s="23"/>
+    </row>
+    <row r="156" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B156" s="13" t="s">
         <v>13</v>
       </c>
@@ -5233,12 +4193,12 @@
       <c r="G156" s="19">
         <v>2.1520811428850282</v>
       </c>
-      <c r="H156" s="40"/>
-      <c r="I156" s="40"/>
-      <c r="J156" s="40"/>
-      <c r="K156" s="40"/>
-    </row>
-    <row r="157" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H156" s="23"/>
+      <c r="I156" s="23"/>
+      <c r="J156" s="23"/>
+      <c r="K156" s="23"/>
+    </row>
+    <row r="157" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B157" s="13" t="s">
         <v>14</v>
       </c>
@@ -5257,12 +4217,12 @@
       <c r="G157" s="19">
         <v>2.2395724823015377</v>
       </c>
-      <c r="H157" s="40"/>
-      <c r="I157" s="40"/>
-      <c r="J157" s="40"/>
-      <c r="K157" s="40"/>
-    </row>
-    <row r="158" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H157" s="23"/>
+      <c r="I157" s="23"/>
+      <c r="J157" s="23"/>
+      <c r="K157" s="23"/>
+    </row>
+    <row r="158" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B158" s="13" t="s">
         <v>11</v>
       </c>
@@ -5281,12 +4241,12 @@
       <c r="G158" s="19">
         <v>14.832580244311355</v>
       </c>
-      <c r="H158" s="40"/>
-      <c r="I158" s="40"/>
-      <c r="J158" s="40"/>
-      <c r="K158" s="40"/>
-    </row>
-    <row r="159" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H158" s="23"/>
+      <c r="I158" s="23"/>
+      <c r="J158" s="23"/>
+      <c r="K158" s="23"/>
+    </row>
+    <row r="159" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B159" s="13" t="s">
         <v>13</v>
       </c>
@@ -5305,12 +4265,12 @@
       <c r="G159" s="19">
         <v>14.987098073326122</v>
       </c>
-      <c r="H159" s="40"/>
-      <c r="I159" s="40"/>
-      <c r="J159" s="40"/>
-      <c r="K159" s="40"/>
-    </row>
-    <row r="160" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H159" s="23"/>
+      <c r="I159" s="23"/>
+      <c r="J159" s="23"/>
+      <c r="K159" s="23"/>
+    </row>
+    <row r="160" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B160" s="13" t="s">
         <v>14</v>
       </c>
@@ -5329,12 +4289,12 @@
       <c r="G160" s="19">
         <v>29.932105574049857</v>
       </c>
-      <c r="H160" s="40"/>
-      <c r="I160" s="40"/>
-      <c r="J160" s="40"/>
-      <c r="K160" s="40"/>
-    </row>
-    <row r="161" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H160" s="23"/>
+      <c r="I160" s="23"/>
+      <c r="J160" s="23"/>
+      <c r="K160" s="23"/>
+    </row>
+    <row r="161" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B161" s="13" t="s">
         <v>11</v>
       </c>
@@ -5353,12 +4313,12 @@
       <c r="G161" s="19">
         <v>42.516320881828612</v>
       </c>
-      <c r="H161" s="40"/>
-      <c r="I161" s="40"/>
-      <c r="J161" s="40"/>
-      <c r="K161" s="40"/>
-    </row>
-    <row r="162" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H161" s="23"/>
+      <c r="I161" s="23"/>
+      <c r="J161" s="23"/>
+      <c r="K161" s="23"/>
+    </row>
+    <row r="162" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="13" t="s">
         <v>13</v>
       </c>
@@ -5377,12 +4337,12 @@
       <c r="G162" s="19">
         <v>41.552107480163023</v>
       </c>
-      <c r="H162" s="40"/>
-      <c r="I162" s="40"/>
-      <c r="J162" s="40"/>
-      <c r="K162" s="40"/>
-    </row>
-    <row r="163" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H162" s="23"/>
+      <c r="I162" s="23"/>
+      <c r="J162" s="23"/>
+      <c r="K162" s="23"/>
+    </row>
+    <row r="163" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B163" s="13" t="s">
         <v>14</v>
       </c>
@@ -5401,12 +4361,12 @@
       <c r="G163" s="19">
         <v>36.875260155014551</v>
       </c>
-      <c r="H163" s="40"/>
-      <c r="I163" s="40"/>
-      <c r="J163" s="40"/>
-      <c r="K163" s="40"/>
-    </row>
-    <row r="164" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H163" s="23"/>
+      <c r="I163" s="23"/>
+      <c r="J163" s="23"/>
+      <c r="K163" s="23"/>
+    </row>
+    <row r="164" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B164" s="13" t="s">
         <v>11</v>
       </c>
@@ -5425,12 +4385,12 @@
       <c r="G164" s="19">
         <v>38.185158300335011</v>
       </c>
-      <c r="H164" s="40"/>
-      <c r="I164" s="40"/>
-      <c r="J164" s="40"/>
-      <c r="K164" s="40"/>
-    </row>
-    <row r="165" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H164" s="23"/>
+      <c r="I164" s="23"/>
+      <c r="J164" s="23"/>
+      <c r="K164" s="23"/>
+    </row>
+    <row r="165" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B165" s="13" t="s">
         <v>13</v>
       </c>
@@ -5449,12 +4409,12 @@
       <c r="G165" s="19">
         <v>41.308714807925448</v>
       </c>
-      <c r="H165" s="40"/>
-      <c r="I165" s="40"/>
-      <c r="J165" s="40"/>
-      <c r="K165" s="40"/>
-    </row>
-    <row r="166" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H165" s="23"/>
+      <c r="I165" s="23"/>
+      <c r="J165" s="23"/>
+      <c r="K165" s="23"/>
+    </row>
+    <row r="166" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B166" s="13" t="s">
         <v>14</v>
       </c>
@@ -5473,12 +4433,12 @@
       <c r="G166" s="19">
         <v>30.953061788634063</v>
       </c>
-      <c r="H166" s="40"/>
-      <c r="I166" s="40"/>
-      <c r="J166" s="40"/>
-      <c r="K166" s="40"/>
-    </row>
-    <row r="167" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H166" s="23"/>
+      <c r="I166" s="23"/>
+      <c r="J166" s="23"/>
+      <c r="K166" s="23"/>
+    </row>
+    <row r="167" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B167" s="13" t="s">
         <v>11</v>
       </c>
@@ -5497,12 +4457,12 @@
       <c r="G167" s="19">
         <v>4.212473377535928</v>
       </c>
-      <c r="H167" s="40"/>
-      <c r="I167" s="40"/>
-      <c r="J167" s="40"/>
-      <c r="K167" s="40"/>
-    </row>
-    <row r="168" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H167" s="23"/>
+      <c r="I167" s="23"/>
+      <c r="J167" s="23"/>
+      <c r="K167" s="23"/>
+    </row>
+    <row r="168" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B168" s="13" t="s">
         <v>13</v>
       </c>
@@ -5521,12 +4481,12 @@
       <c r="G168" s="19">
         <v>2.0962607986382698</v>
       </c>
-      <c r="H168" s="40"/>
-      <c r="I168" s="40"/>
-      <c r="J168" s="40"/>
-      <c r="K168" s="40"/>
-    </row>
-    <row r="169" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H168" s="23"/>
+      <c r="I168" s="23"/>
+      <c r="J168" s="23"/>
+      <c r="K168" s="23"/>
+    </row>
+    <row r="169" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B169" s="13" t="s">
         <v>14</v>
       </c>
@@ -5545,12 +4505,12 @@
       <c r="G169" s="19">
         <v>2.256034883631453</v>
       </c>
-      <c r="H169" s="40"/>
-      <c r="I169" s="40"/>
-      <c r="J169" s="40"/>
-      <c r="K169" s="40"/>
-    </row>
-    <row r="170" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H169" s="23"/>
+      <c r="I169" s="23"/>
+      <c r="J169" s="23"/>
+      <c r="K169" s="23"/>
+    </row>
+    <row r="170" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B170" s="13" t="s">
         <v>11</v>
       </c>
@@ -5569,12 +4529,12 @@
       <c r="G170" s="19">
         <v>15.807439824541817</v>
       </c>
-      <c r="H170" s="40"/>
-      <c r="I170" s="40"/>
-      <c r="J170" s="40"/>
-      <c r="K170" s="40"/>
-    </row>
-    <row r="171" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H170" s="23"/>
+      <c r="I170" s="23"/>
+      <c r="J170" s="23"/>
+      <c r="K170" s="23"/>
+    </row>
+    <row r="171" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B171" s="13" t="s">
         <v>13</v>
       </c>
@@ -5593,12 +4553,12 @@
       <c r="G171" s="19">
         <v>16.354891769290095</v>
       </c>
-      <c r="H171" s="40"/>
-      <c r="I171" s="40"/>
-      <c r="J171" s="40"/>
-      <c r="K171" s="40"/>
-    </row>
-    <row r="172" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H171" s="23"/>
+      <c r="I171" s="23"/>
+      <c r="J171" s="23"/>
+      <c r="K171" s="23"/>
+    </row>
+    <row r="172" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B172" s="13" t="s">
         <v>14</v>
       </c>
@@ -5617,12 +4577,12 @@
       <c r="G172" s="19">
         <v>31.29188612194876</v>
       </c>
-      <c r="H172" s="40"/>
-      <c r="I172" s="40"/>
-      <c r="J172" s="40"/>
-      <c r="K172" s="40"/>
-    </row>
-    <row r="173" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H172" s="23"/>
+      <c r="I172" s="23"/>
+      <c r="J172" s="23"/>
+      <c r="K172" s="23"/>
+    </row>
+    <row r="173" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B173" s="13" t="s">
         <v>11</v>
       </c>
@@ -5641,12 +4601,12 @@
       <c r="G173" s="19">
         <v>42.935690378887422</v>
       </c>
-      <c r="H173" s="40"/>
-      <c r="I173" s="40"/>
-      <c r="J173" s="40"/>
-      <c r="K173" s="40"/>
-    </row>
-    <row r="174" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H173" s="23"/>
+      <c r="I173" s="23"/>
+      <c r="J173" s="23"/>
+      <c r="K173" s="23"/>
+    </row>
+    <row r="174" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" s="13" t="s">
         <v>13</v>
       </c>
@@ -5665,12 +4625,12 @@
       <c r="G174" s="19">
         <v>41.623986072728655</v>
       </c>
-      <c r="H174" s="40"/>
-      <c r="I174" s="40"/>
-      <c r="J174" s="40"/>
-      <c r="K174" s="40"/>
-    </row>
-    <row r="175" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H174" s="23"/>
+      <c r="I174" s="23"/>
+      <c r="J174" s="23"/>
+      <c r="K174" s="23"/>
+    </row>
+    <row r="175" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B175" s="13" t="s">
         <v>14</v>
       </c>
@@ -5689,12 +4649,12 @@
       <c r="G175" s="19">
         <v>36.24574287597239</v>
       </c>
-      <c r="H175" s="40"/>
-      <c r="I175" s="40"/>
-      <c r="J175" s="40"/>
-      <c r="K175" s="40"/>
-    </row>
-    <row r="176" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H175" s="23"/>
+      <c r="I175" s="23"/>
+      <c r="J175" s="23"/>
+      <c r="K175" s="23"/>
+    </row>
+    <row r="176" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B176" s="13" t="s">
         <v>11</v>
       </c>
@@ -5713,12 +4673,12 @@
       <c r="G176" s="19">
         <v>37.04439641903484</v>
       </c>
-      <c r="H176" s="40"/>
-      <c r="I176" s="40"/>
-      <c r="J176" s="40"/>
-      <c r="K176" s="40"/>
-    </row>
-    <row r="177" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H176" s="23"/>
+      <c r="I176" s="23"/>
+      <c r="J176" s="23"/>
+      <c r="K176" s="23"/>
+    </row>
+    <row r="177" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B177" s="13" t="s">
         <v>13</v>
       </c>
@@ -5737,12 +4697,12 @@
       <c r="G177" s="19">
         <v>39.92486135934297</v>
       </c>
-      <c r="H177" s="40"/>
-      <c r="I177" s="40"/>
-      <c r="J177" s="40"/>
-      <c r="K177" s="40"/>
-    </row>
-    <row r="178" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H177" s="23"/>
+      <c r="I177" s="23"/>
+      <c r="J177" s="23"/>
+      <c r="K177" s="23"/>
+    </row>
+    <row r="178" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B178" s="13" t="s">
         <v>14</v>
       </c>
@@ -5761,12 +4721,12 @@
       <c r="G178" s="19">
         <v>30.206336118447407</v>
       </c>
-      <c r="H178" s="40"/>
-      <c r="I178" s="40"/>
-      <c r="J178" s="40"/>
-      <c r="K178" s="40"/>
-    </row>
-    <row r="179" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H178" s="23"/>
+      <c r="I178" s="23"/>
+      <c r="J178" s="23"/>
+      <c r="K178" s="23"/>
+    </row>
+    <row r="179" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" s="13" t="s">
         <v>11</v>
       </c>
@@ -5785,12 +4745,12 @@
       <c r="G179" s="19">
         <v>4.0130045470776761</v>
       </c>
-      <c r="H179" s="40"/>
-      <c r="I179" s="40"/>
-      <c r="J179" s="40"/>
-      <c r="K179" s="40"/>
-    </row>
-    <row r="180" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H179" s="23"/>
+      <c r="I179" s="23"/>
+      <c r="J179" s="23"/>
+      <c r="K179" s="23"/>
+    </row>
+    <row r="180" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B180" s="13" t="s">
         <v>13</v>
       </c>
@@ -5809,12 +4769,12 @@
       <c r="G180" s="19">
         <v>2.0295387562309761</v>
       </c>
-      <c r="H180" s="40"/>
-      <c r="I180" s="40"/>
-      <c r="J180" s="40"/>
-      <c r="K180" s="40"/>
-    </row>
-    <row r="181" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H180" s="23"/>
+      <c r="I180" s="23"/>
+      <c r="J180" s="23"/>
+      <c r="K180" s="23"/>
+    </row>
+    <row r="181" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B181" s="13" t="s">
         <v>14</v>
       </c>
@@ -5833,12 +4793,12 @@
       <c r="G181" s="19">
         <v>2.4340313526480446</v>
       </c>
-      <c r="H181" s="40"/>
-      <c r="I181" s="40"/>
-      <c r="J181" s="40"/>
-      <c r="K181" s="40"/>
-    </row>
-    <row r="182" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H181" s="23"/>
+      <c r="I181" s="23"/>
+      <c r="J181" s="23"/>
+      <c r="K181" s="23"/>
+    </row>
+    <row r="182" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B182" s="13" t="s">
         <v>11</v>
       </c>
@@ -5857,12 +4817,12 @@
       <c r="G182" s="19">
         <v>16.566739202865495</v>
       </c>
-      <c r="H182" s="40"/>
-      <c r="I182" s="40"/>
-      <c r="J182" s="40"/>
-      <c r="K182" s="40"/>
-    </row>
-    <row r="183" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H182" s="23"/>
+      <c r="I182" s="23"/>
+      <c r="J182" s="23"/>
+      <c r="K182" s="23"/>
+    </row>
+    <row r="183" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B183" s="13" t="s">
         <v>13</v>
       </c>
@@ -5881,12 +4841,12 @@
       <c r="G183" s="19">
         <v>17.441975232910607</v>
       </c>
-      <c r="H183" s="40"/>
-      <c r="I183" s="40"/>
-      <c r="J183" s="40"/>
-      <c r="K183" s="40"/>
-    </row>
-    <row r="184" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H183" s="23"/>
+      <c r="I183" s="23"/>
+      <c r="J183" s="23"/>
+      <c r="K183" s="23"/>
+    </row>
+    <row r="184" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B184" s="13" t="s">
         <v>14</v>
       </c>
@@ -5905,12 +4865,12 @@
       <c r="G184" s="19">
         <v>32.395993772894002</v>
       </c>
-      <c r="H184" s="40"/>
-      <c r="I184" s="40"/>
-      <c r="J184" s="40"/>
-      <c r="K184" s="40"/>
-    </row>
-    <row r="185" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H184" s="23"/>
+      <c r="I184" s="23"/>
+      <c r="J184" s="23"/>
+      <c r="K184" s="23"/>
+    </row>
+    <row r="185" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="13" t="s">
         <v>11</v>
       </c>
@@ -5929,12 +4889,12 @@
       <c r="G185" s="19">
         <v>45.442191661809403</v>
       </c>
-      <c r="H185" s="40"/>
-      <c r="I185" s="40"/>
-      <c r="J185" s="40"/>
-      <c r="K185" s="40"/>
-    </row>
-    <row r="186" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H185" s="23"/>
+      <c r="I185" s="23"/>
+      <c r="J185" s="23"/>
+      <c r="K185" s="23"/>
+    </row>
+    <row r="186" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B186" s="13" t="s">
         <v>13</v>
       </c>
@@ -5953,12 +4913,12 @@
       <c r="G186" s="19">
         <v>40.655984644352053</v>
       </c>
-      <c r="H186" s="40"/>
-      <c r="I186" s="40"/>
-      <c r="J186" s="40"/>
-      <c r="K186" s="40"/>
-    </row>
-    <row r="187" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H186" s="23"/>
+      <c r="I186" s="23"/>
+      <c r="J186" s="23"/>
+      <c r="K186" s="23"/>
+    </row>
+    <row r="187" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B187" s="13" t="s">
         <v>14</v>
       </c>
@@ -5977,12 +4937,12 @@
       <c r="G187" s="19">
         <v>36.153080816467799</v>
       </c>
-      <c r="H187" s="40"/>
-      <c r="I187" s="40"/>
-      <c r="J187" s="40"/>
-      <c r="K187" s="40"/>
-    </row>
-    <row r="188" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H187" s="23"/>
+      <c r="I187" s="23"/>
+      <c r="J187" s="23"/>
+      <c r="K187" s="23"/>
+    </row>
+    <row r="188" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B188" s="13" t="s">
         <v>11</v>
       </c>
@@ -6001,12 +4961,12 @@
       <c r="G188" s="19">
         <v>33.978064588247413</v>
       </c>
-      <c r="H188" s="40"/>
-      <c r="I188" s="40"/>
-      <c r="J188" s="40"/>
-      <c r="K188" s="40"/>
-    </row>
-    <row r="189" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H188" s="23"/>
+      <c r="I188" s="23"/>
+      <c r="J188" s="23"/>
+      <c r="K188" s="23"/>
+    </row>
+    <row r="189" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" s="13" t="s">
         <v>13</v>
       </c>
@@ -6025,12 +4985,12 @@
       <c r="G189" s="19">
         <v>39.872501366506377</v>
       </c>
-      <c r="H189" s="40"/>
-      <c r="I189" s="40"/>
-      <c r="J189" s="40"/>
-      <c r="K189" s="40"/>
-    </row>
-    <row r="190" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H189" s="23"/>
+      <c r="I189" s="23"/>
+      <c r="J189" s="23"/>
+      <c r="K189" s="23"/>
+    </row>
+    <row r="190" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="13" t="s">
         <v>14</v>
       </c>
@@ -6049,12 +5009,12 @@
       <c r="G190" s="19">
         <v>29.01689405799015</v>
       </c>
-      <c r="H190" s="40"/>
-      <c r="I190" s="40"/>
-      <c r="J190" s="40"/>
-      <c r="K190" s="40"/>
-    </row>
-    <row r="191" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H190" s="23"/>
+      <c r="I190" s="23"/>
+      <c r="J190" s="23"/>
+      <c r="K190" s="23"/>
+    </row>
+    <row r="191" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="13" t="s">
         <v>11</v>
       </c>
@@ -6073,12 +5033,12 @@
       <c r="G191" s="19">
         <v>3.2074704928078637</v>
       </c>
-      <c r="H191" s="40"/>
-      <c r="I191" s="40"/>
-      <c r="J191" s="40"/>
-      <c r="K191" s="40"/>
-    </row>
-    <row r="192" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H191" s="23"/>
+      <c r="I191" s="23"/>
+      <c r="J191" s="23"/>
+      <c r="K191" s="23"/>
+    </row>
+    <row r="192" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="13" t="s">
         <v>13</v>
       </c>
@@ -6097,12 +5057,12 @@
       <c r="G192" s="19">
         <v>2.0578261360582344</v>
       </c>
-      <c r="H192" s="40"/>
-      <c r="I192" s="40"/>
-      <c r="J192" s="40"/>
-      <c r="K192" s="40"/>
-    </row>
-    <row r="193" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H192" s="23"/>
+      <c r="I192" s="23"/>
+      <c r="J192" s="23"/>
+      <c r="K192" s="23"/>
+    </row>
+    <row r="193" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="13" t="s">
         <v>14</v>
       </c>
@@ -6121,12 +5081,12 @@
       <c r="G193" s="19">
         <v>2.0289028621700744</v>
       </c>
-      <c r="H193" s="40"/>
-      <c r="I193" s="40"/>
-      <c r="J193" s="40"/>
-      <c r="K193" s="40"/>
-    </row>
-    <row r="194" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H193" s="23"/>
+      <c r="I193" s="23"/>
+      <c r="J193" s="23"/>
+      <c r="K193" s="23"/>
+    </row>
+    <row r="194" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="13" t="s">
         <v>11</v>
       </c>
@@ -6145,12 +5105,12 @@
       <c r="G194" s="19">
         <v>18.598400098603769</v>
       </c>
-      <c r="H194" s="40"/>
-      <c r="I194" s="40"/>
-      <c r="J194" s="40"/>
-      <c r="K194" s="40"/>
-    </row>
-    <row r="195" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H194" s="23"/>
+      <c r="I194" s="23"/>
+      <c r="J194" s="23"/>
+      <c r="K194" s="23"/>
+    </row>
+    <row r="195" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="13" t="s">
         <v>13</v>
       </c>
@@ -6169,12 +5129,12 @@
       <c r="G195" s="19">
         <v>20.521164844139275</v>
       </c>
-      <c r="H195" s="40"/>
-      <c r="I195" s="40"/>
-      <c r="J195" s="40"/>
-      <c r="K195" s="40"/>
-    </row>
-    <row r="196" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H195" s="23"/>
+      <c r="I195" s="23"/>
+      <c r="J195" s="23"/>
+      <c r="K195" s="23"/>
+    </row>
+    <row r="196" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="13" t="s">
         <v>14</v>
       </c>
@@ -6193,12 +5153,12 @@
       <c r="G196" s="19">
         <v>37.032460972720457</v>
       </c>
-      <c r="H196" s="40"/>
-      <c r="I196" s="40"/>
-      <c r="J196" s="40"/>
-      <c r="K196" s="40"/>
-    </row>
-    <row r="197" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H196" s="23"/>
+      <c r="I196" s="23"/>
+      <c r="J196" s="23"/>
+      <c r="K196" s="23"/>
+    </row>
+    <row r="197" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="13" t="s">
         <v>11</v>
       </c>
@@ -6217,12 +5177,12 @@
       <c r="G197" s="19">
         <v>46.887747105335961</v>
       </c>
-      <c r="H197" s="40"/>
-      <c r="I197" s="40"/>
-      <c r="J197" s="40"/>
-      <c r="K197" s="40"/>
-    </row>
-    <row r="198" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H197" s="23"/>
+      <c r="I197" s="23"/>
+      <c r="J197" s="23"/>
+      <c r="K197" s="23"/>
+    </row>
+    <row r="198" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B198" s="13" t="s">
         <v>13</v>
       </c>
@@ -6241,12 +5201,12 @@
       <c r="G198" s="19">
         <v>42.110964765907347</v>
       </c>
-      <c r="H198" s="40"/>
-      <c r="I198" s="40"/>
-      <c r="J198" s="40"/>
-      <c r="K198" s="40"/>
-    </row>
-    <row r="199" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H198" s="23"/>
+      <c r="I198" s="23"/>
+      <c r="J198" s="23"/>
+      <c r="K198" s="23"/>
+    </row>
+    <row r="199" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B199" s="13" t="s">
         <v>14</v>
       </c>
@@ -6265,12 +5225,12 @@
       <c r="G199" s="19">
         <v>35.067059111920329</v>
       </c>
-      <c r="H199" s="40"/>
-      <c r="I199" s="40"/>
-      <c r="J199" s="40"/>
-      <c r="K199" s="40"/>
-    </row>
-    <row r="200" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H199" s="23"/>
+      <c r="I199" s="23"/>
+      <c r="J199" s="23"/>
+      <c r="K199" s="23"/>
+    </row>
+    <row r="200" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B200" s="13" t="s">
         <v>11</v>
       </c>
@@ -6289,12 +5249,12 @@
       <c r="G200" s="19">
         <v>31.306382303252398</v>
       </c>
-      <c r="H200" s="40"/>
-      <c r="I200" s="40"/>
-      <c r="J200" s="40"/>
-      <c r="K200" s="40"/>
-    </row>
-    <row r="201" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H200" s="23"/>
+      <c r="I200" s="23"/>
+      <c r="J200" s="23"/>
+      <c r="K200" s="23"/>
+    </row>
+    <row r="201" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B201" s="13" t="s">
         <v>13</v>
       </c>
@@ -6313,12 +5273,12 @@
       <c r="G201" s="19">
         <v>35.310044253895157</v>
       </c>
-      <c r="H201" s="40"/>
-      <c r="I201" s="40"/>
-      <c r="J201" s="40"/>
-      <c r="K201" s="40"/>
-    </row>
-    <row r="202" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H201" s="23"/>
+      <c r="I201" s="23"/>
+      <c r="J201" s="23"/>
+      <c r="K201" s="23"/>
+    </row>
+    <row r="202" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B202" s="13" t="s">
         <v>14</v>
       </c>
@@ -6337,12 +5297,12 @@
       <c r="G202" s="19">
         <v>25.871577053189139</v>
       </c>
-      <c r="H202" s="40"/>
-      <c r="I202" s="40"/>
-      <c r="J202" s="40"/>
-      <c r="K202" s="40"/>
-    </row>
-    <row r="203" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H202" s="23"/>
+      <c r="I202" s="23"/>
+      <c r="J202" s="23"/>
+      <c r="K202" s="23"/>
+    </row>
+    <row r="203" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B203" s="13" t="s">
         <v>11</v>
       </c>
@@ -6362,7 +5322,7 @@
         <v>3.2871763022626288</v>
       </c>
     </row>
-    <row r="204" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B204" s="13" t="s">
         <v>13</v>
       </c>
@@ -6382,7 +5342,7 @@
         <v>2.0206492308206041</v>
       </c>
     </row>
-    <row r="205" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B205" s="13" t="s">
         <v>14</v>
       </c>
@@ -6401,12 +5361,12 @@
       <c r="G205" s="19">
         <v>1.8955267408437952</v>
       </c>
-      <c r="H205" s="41"/>
-      <c r="I205" s="41"/>
-      <c r="J205" s="41"/>
-      <c r="K205" s="41"/>
-    </row>
-    <row r="206" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H205" s="24"/>
+      <c r="I205" s="24"/>
+      <c r="J205" s="24"/>
+      <c r="K205" s="24"/>
+    </row>
+    <row r="206" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="13" t="s">
         <v>11</v>
       </c>
@@ -6425,12 +5385,12 @@
       <c r="G206" s="19">
         <v>19.922748939855431</v>
       </c>
-      <c r="H206" s="42"/>
-      <c r="I206" s="43"/>
-      <c r="J206" s="43"/>
-      <c r="K206" s="43"/>
-    </row>
-    <row r="207" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H206" s="25"/>
+      <c r="I206" s="26"/>
+      <c r="J206" s="26"/>
+      <c r="K206" s="26"/>
+    </row>
+    <row r="207" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" s="13" t="s">
         <v>13</v>
       </c>
@@ -6449,12 +5409,12 @@
       <c r="G207" s="19">
         <v>20.900404328738102</v>
       </c>
-      <c r="H207" s="44"/>
-      <c r="I207" s="44"/>
-      <c r="J207" s="44"/>
-      <c r="K207" s="43"/>
-    </row>
-    <row r="208" spans="2:11" s="39" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H207" s="27"/>
+      <c r="I207" s="27"/>
+      <c r="J207" s="27"/>
+      <c r="K207" s="26"/>
+    </row>
+    <row r="208" spans="2:11" s="22" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B208" s="13" t="s">
         <v>14</v>
       </c>
@@ -6473,12 +5433,12 @@
       <c r="G208" s="19">
         <v>37.913580679775841</v>
       </c>
-      <c r="H208" s="44"/>
-      <c r="I208" s="44"/>
-      <c r="J208" s="44"/>
-      <c r="K208" s="43"/>
-    </row>
-    <row r="209" spans="2:11" s="39" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H208" s="27"/>
+      <c r="I208" s="27"/>
+      <c r="J208" s="27"/>
+      <c r="K208" s="26"/>
+    </row>
+    <row r="209" spans="2:11" s="22" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B209" s="13" t="s">
         <v>11</v>
       </c>
@@ -6497,12 +5457,12 @@
       <c r="G209" s="19">
         <v>44.455143881036122</v>
       </c>
-      <c r="H209" s="44"/>
-      <c r="I209" s="44"/>
-      <c r="J209" s="44"/>
-      <c r="K209" s="45"/>
-    </row>
-    <row r="210" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H209" s="27"/>
+      <c r="I209" s="27"/>
+      <c r="J209" s="27"/>
+      <c r="K209" s="28"/>
+    </row>
+    <row r="210" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B210" s="13" t="s">
         <v>13</v>
       </c>
@@ -6521,12 +5481,12 @@
       <c r="G210" s="19">
         <v>40.484810767756208</v>
       </c>
-      <c r="H210" s="45"/>
-      <c r="I210" s="45"/>
-      <c r="J210" s="45"/>
-      <c r="K210" s="45"/>
-    </row>
-    <row r="211" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H210" s="28"/>
+      <c r="I210" s="28"/>
+      <c r="J210" s="28"/>
+      <c r="K210" s="28"/>
+    </row>
+    <row r="211" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B211" s="13" t="s">
         <v>14</v>
       </c>
@@ -6545,12 +5505,12 @@
       <c r="G211" s="19">
         <v>34.248790746127099</v>
       </c>
-      <c r="H211" s="45"/>
-      <c r="I211" s="45"/>
-      <c r="J211" s="45"/>
-      <c r="K211" s="45"/>
-    </row>
-    <row r="212" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H211" s="28"/>
+      <c r="I211" s="28"/>
+      <c r="J211" s="28"/>
+      <c r="K211" s="28"/>
+    </row>
+    <row r="212" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B212" s="13" t="s">
         <v>11</v>
       </c>
@@ -6569,12 +5529,12 @@
       <c r="G212" s="19">
         <v>32.334930876845824</v>
       </c>
-      <c r="H212" s="45"/>
-      <c r="I212" s="45"/>
-      <c r="J212" s="45"/>
-      <c r="K212" s="45"/>
-    </row>
-    <row r="213" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H212" s="28"/>
+      <c r="I212" s="28"/>
+      <c r="J212" s="28"/>
+      <c r="K212" s="28"/>
+    </row>
+    <row r="213" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B213" s="13" t="s">
         <v>13</v>
       </c>
@@ -6594,7 +5554,7 @@
         <v>36.594135672685091</v>
       </c>
     </row>
-    <row r="214" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B214" s="13" t="s">
         <v>14</v>
       </c>
@@ -6614,117 +5574,117 @@
         <v>25.942101833253261</v>
       </c>
     </row>
-    <row r="215" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D215" s="46" t="s">
+    <row r="215" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D215" s="29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B216" s="47"/>
-      <c r="D216" s="46"/>
-    </row>
-    <row r="217" spans="2:11" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="48" t="s">
+    <row r="216" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B216" s="30"/>
+      <c r="D216" s="29"/>
+    </row>
+    <row r="217" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C217" s="48"/>
-      <c r="D217" s="48"/>
-      <c r="E217" s="48"/>
-      <c r="F217" s="48"/>
-      <c r="G217" s="48"/>
-    </row>
-    <row r="218" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="49" t="s">
+      <c r="C217" s="31"/>
+      <c r="D217" s="31"/>
+      <c r="E217" s="31"/>
+      <c r="F217" s="31"/>
+      <c r="G217" s="31"/>
+    </row>
+    <row r="218" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C218" s="42"/>
-      <c r="D218" s="50"/>
-      <c r="E218" s="42"/>
-      <c r="F218" s="42"/>
-      <c r="G218" s="42"/>
-    </row>
-    <row r="219" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="51" t="s">
+      <c r="C218" s="25"/>
+      <c r="D218" s="33"/>
+      <c r="E218" s="25"/>
+      <c r="F218" s="25"/>
+      <c r="G218" s="25"/>
+    </row>
+    <row r="219" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C219" s="51"/>
-      <c r="D219" s="51"/>
-      <c r="E219" s="51"/>
-      <c r="F219" s="51"/>
-      <c r="G219" s="51"/>
-    </row>
-    <row r="220" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="51"/>
-      <c r="C220" s="51"/>
-      <c r="D220" s="51"/>
-      <c r="E220" s="51"/>
-      <c r="F220" s="51"/>
-      <c r="G220" s="51"/>
-    </row>
-    <row r="221" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B221" s="51" t="s">
+      <c r="C219" s="34"/>
+      <c r="D219" s="34"/>
+      <c r="E219" s="34"/>
+      <c r="F219" s="34"/>
+      <c r="G219" s="34"/>
+    </row>
+    <row r="220" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="34"/>
+      <c r="C220" s="34"/>
+      <c r="D220" s="34"/>
+      <c r="E220" s="34"/>
+      <c r="F220" s="34"/>
+      <c r="G220" s="34"/>
+    </row>
+    <row r="221" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B221" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C221" s="51"/>
-      <c r="D221" s="51"/>
-      <c r="E221" s="51"/>
-      <c r="F221" s="51"/>
-      <c r="G221" s="51"/>
-    </row>
-    <row r="222" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B222" s="52" t="s">
+      <c r="C221" s="34"/>
+      <c r="D221" s="34"/>
+      <c r="E221" s="34"/>
+      <c r="F221" s="34"/>
+      <c r="G221" s="34"/>
+    </row>
+    <row r="222" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B222" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C222" s="53"/>
-      <c r="D222" s="54"/>
-      <c r="E222" s="53"/>
-      <c r="F222" s="53"/>
-      <c r="G222" s="53"/>
-    </row>
-    <row r="223" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B223" s="53"/>
-      <c r="C223" s="53"/>
-      <c r="D223" s="54"/>
-      <c r="E223" s="53"/>
-      <c r="F223" s="53"/>
-      <c r="G223" s="53"/>
-    </row>
-    <row r="224" spans="2:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B224" s="49" t="s">
+      <c r="C222" s="36"/>
+      <c r="D222" s="37"/>
+      <c r="E222" s="36"/>
+      <c r="F222" s="36"/>
+      <c r="G222" s="36"/>
+    </row>
+    <row r="223" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="36"/>
+      <c r="C223" s="36"/>
+      <c r="D223" s="37"/>
+      <c r="E223" s="36"/>
+      <c r="F223" s="36"/>
+      <c r="G223" s="36"/>
+    </row>
+    <row r="224" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B224" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C224" s="55"/>
-      <c r="D224" s="56"/>
-      <c r="E224" s="45"/>
-      <c r="F224" s="45"/>
-      <c r="G224" s="45"/>
-    </row>
-    <row r="225" spans="2:4" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D225" s="46"/>
-    </row>
-    <row r="226" spans="2:4" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B226" s="49" t="s">
+      <c r="C224" s="38"/>
+      <c r="D224" s="39"/>
+      <c r="E224" s="28"/>
+      <c r="F224" s="28"/>
+      <c r="G224" s="28"/>
+    </row>
+    <row r="225" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D225" s="29"/>
+    </row>
+    <row r="226" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B226" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D226" s="46"/>
-    </row>
-    <row r="227" spans="2:4" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B227" s="49" t="s">
+      <c r="D226" s="29"/>
+    </row>
+    <row r="227" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B227" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D227" s="46"/>
-    </row>
-    <row r="228" spans="2:4" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B228" s="49" t="s">
+      <c r="D227" s="29"/>
+    </row>
+    <row r="228" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B228" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D228" s="46"/>
-    </row>
-    <row r="229" spans="2:4" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B229" s="57" t="s">
+      <c r="D228" s="29"/>
+    </row>
+    <row r="229" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B229" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D229" s="46"/>
+      <c r="D229" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/assets/excel/2026_4-1-3.xlsx
+++ b/assets/excel/2026_4-1-3.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BiesterChristophLSN\Desktop\MZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC47C1A-FD32-483F-A27C-21E8ACA559FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EC4A073-03C2-4EAB-89DA-F1E3358B5EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{95AE330F-3948-45C2-BEAB-3D17B9280608}"/>
+    <workbookView xWindow="20052" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AE330F-3948-45C2-BEAB-3D17B9280608}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -107,9 +107,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
-  </si>
-  <si>
     <t>2) Ohne Abschluss einschließlich Abschluss Förderschule</t>
   </si>
   <si>
@@ -138,6 +135,9 @@
   </si>
   <si>
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
+  </si>
+  <si>
+    <t>1) Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
   </si>
 </sst>
 </file>
@@ -468,17 +468,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -547,6 +541,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -567,9 +567,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -607,7 +607,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -713,7 +713,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -855,7 +855,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -864,7 +864,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3510A80F-E3AE-46B7-BA8F-8173D0D9C665}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="B1:L229"/>
+  <dimension ref="B1:P228"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -878,7 +878,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -913,28 +913,28 @@
       <c r="L4" s="1"/>
     </row>
     <row r="6" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="54"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="42"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="51"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="49"/>
       <c r="F7" s="8" t="s">
         <v>7</v>
       </c>
@@ -943,24 +943,24 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="55" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="53"/>
+      <c r="G8" s="51"/>
     </row>
     <row r="9" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="43"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="56" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
     </row>
     <row r="10" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
@@ -5438,7 +5438,7 @@
       <c r="J208" s="27"/>
       <c r="K208" s="26"/>
     </row>
-    <row r="209" spans="2:11" s="22" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:16" s="22" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B209" s="13" t="s">
         <v>11</v>
       </c>
@@ -5462,7 +5462,7 @@
       <c r="J209" s="27"/>
       <c r="K209" s="28"/>
     </row>
-    <row r="210" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B210" s="13" t="s">
         <v>13</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="J210" s="28"/>
       <c r="K210" s="28"/>
     </row>
-    <row r="211" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B211" s="13" t="s">
         <v>14</v>
       </c>
@@ -5510,7 +5510,7 @@
       <c r="J211" s="28"/>
       <c r="K211" s="28"/>
     </row>
-    <row r="212" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B212" s="13" t="s">
         <v>11</v>
       </c>
@@ -5534,7 +5534,7 @@
       <c r="J212" s="28"/>
       <c r="K212" s="28"/>
     </row>
-    <row r="213" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B213" s="13" t="s">
         <v>13</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>36.594135672685091</v>
       </c>
     </row>
-    <row r="214" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B214" s="13" t="s">
         <v>14</v>
       </c>
@@ -5574,120 +5574,142 @@
         <v>25.942101833253261</v>
       </c>
     </row>
-    <row r="215" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D215" s="29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B216" s="30"/>
       <c r="D216" s="29"/>
     </row>
-    <row r="217" spans="2:11" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="31" t="s">
+    <row r="217" spans="2:16" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C217" s="56"/>
+      <c r="D217" s="56"/>
+      <c r="E217" s="56"/>
+      <c r="F217" s="56"/>
+      <c r="G217" s="56"/>
+      <c r="H217" s="56"/>
+      <c r="I217" s="56"/>
+      <c r="J217" s="56"/>
+      <c r="K217" s="56"/>
+      <c r="L217" s="56"/>
+      <c r="M217" s="56"/>
+      <c r="N217" s="56"/>
+      <c r="O217" s="56"/>
+      <c r="P217" s="56"/>
+    </row>
+    <row r="218" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C217" s="31"/>
-      <c r="D217" s="31"/>
-      <c r="E217" s="31"/>
-      <c r="F217" s="31"/>
-      <c r="G217" s="31"/>
-    </row>
-    <row r="218" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="32" t="s">
-        <v>20</v>
-      </c>
       <c r="C218" s="25"/>
-      <c r="D218" s="33"/>
+      <c r="D218" s="32"/>
       <c r="E218" s="25"/>
       <c r="F218" s="25"/>
       <c r="G218" s="25"/>
     </row>
-    <row r="219" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="34" t="s">
+    <row r="219" spans="2:16" s="22" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" s="57"/>
+      <c r="D219" s="57"/>
+      <c r="E219" s="57"/>
+      <c r="F219" s="57"/>
+      <c r="G219" s="57"/>
+      <c r="H219" s="57"/>
+      <c r="I219" s="57"/>
+      <c r="J219" s="57"/>
+      <c r="K219" s="57"/>
+      <c r="L219" s="57"/>
+      <c r="M219" s="57"/>
+      <c r="N219" s="57"/>
+      <c r="O219" s="57"/>
+      <c r="P219" s="57"/>
+    </row>
+    <row r="220" spans="2:16" s="22" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C219" s="34"/>
-      <c r="D219" s="34"/>
-      <c r="E219" s="34"/>
-      <c r="F219" s="34"/>
-      <c r="G219" s="34"/>
-    </row>
-    <row r="220" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="34"/>
-      <c r="C220" s="34"/>
-      <c r="D220" s="34"/>
-      <c r="E220" s="34"/>
-      <c r="F220" s="34"/>
-      <c r="G220" s="34"/>
-    </row>
-    <row r="221" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B221" s="34" t="s">
+      <c r="C220" s="57"/>
+      <c r="D220" s="57"/>
+      <c r="E220" s="57"/>
+      <c r="F220" s="57"/>
+      <c r="G220" s="57"/>
+      <c r="H220" s="57"/>
+      <c r="I220" s="57"/>
+      <c r="J220" s="57"/>
+      <c r="K220" s="57"/>
+      <c r="L220" s="57"/>
+      <c r="M220" s="57"/>
+      <c r="N220" s="57"/>
+      <c r="O220" s="57"/>
+      <c r="P220" s="57"/>
+    </row>
+    <row r="221" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B221" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C221" s="34"/>
-      <c r="D221" s="34"/>
+      <c r="D221" s="35"/>
       <c r="E221" s="34"/>
       <c r="F221" s="34"/>
       <c r="G221" s="34"/>
     </row>
-    <row r="222" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B222" s="35" t="s">
+    <row r="222" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B222" s="34"/>
+      <c r="C222" s="34"/>
+      <c r="D222" s="35"/>
+      <c r="E222" s="34"/>
+      <c r="F222" s="34"/>
+      <c r="G222" s="34"/>
+    </row>
+    <row r="223" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C222" s="36"/>
-      <c r="D222" s="37"/>
-      <c r="E222" s="36"/>
-      <c r="F222" s="36"/>
-      <c r="G222" s="36"/>
-    </row>
-    <row r="223" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B223" s="36"/>
       <c r="C223" s="36"/>
       <c r="D223" s="37"/>
-      <c r="E223" s="36"/>
-      <c r="F223" s="36"/>
-      <c r="G223" s="36"/>
-    </row>
-    <row r="224" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B224" s="32" t="s">
+      <c r="E223" s="28"/>
+      <c r="F223" s="28"/>
+      <c r="G223" s="28"/>
+    </row>
+    <row r="224" spans="2:16" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D224" s="29"/>
+    </row>
+    <row r="225" spans="2:4" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C224" s="38"/>
-      <c r="D224" s="39"/>
-      <c r="E224" s="28"/>
-      <c r="F224" s="28"/>
-      <c r="G224" s="28"/>
-    </row>
-    <row r="225" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D225" s="29"/>
     </row>
-    <row r="226" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B226" s="32" t="s">
+    <row r="226" spans="2:4" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B226" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D226" s="29"/>
+    </row>
+    <row r="227" spans="2:4" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B227" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D226" s="29"/>
-    </row>
-    <row r="227" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B227" s="32" t="s">
-        <v>28</v>
-      </c>
       <c r="D227" s="29"/>
     </row>
-    <row r="228" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B228" s="32" t="s">
+    <row r="228" spans="2:4" s="22" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B228" s="38" t="s">
         <v>26</v>
       </c>
       <c r="D228" s="29"/>
     </row>
-    <row r="229" spans="2:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B229" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D229" s="29"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="B217:P217"/>
+    <mergeCell ref="B219:P219"/>
+    <mergeCell ref="B220:P220"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D6:D9"/>
@@ -5697,8 +5719,8 @@
     <mergeCell ref="E9:G9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B229" r:id="rId1" xr:uid="{0178E4F1-5847-4B81-ADBB-EFDE3517656C}"/>
-    <hyperlink ref="B222" r:id="rId2" xr:uid="{4B446814-EB3D-4088-8F8C-638339A7752C}"/>
+    <hyperlink ref="B228" r:id="rId1" xr:uid="{0178E4F1-5847-4B81-ADBB-EFDE3517656C}"/>
+    <hyperlink ref="B221" r:id="rId2" xr:uid="{4B446814-EB3D-4088-8F8C-638339A7752C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
